--- a/assets/frm-eib04-template.xlsx
+++ b/assets/frm-eib04-template.xlsx
@@ -12,11 +12,11 @@
     <workbookView xWindow="32760" yWindow="330" windowWidth="12120" windowHeight="7680" tabRatio="599"/>
   </bookViews>
   <sheets>
-    <sheet name="WRM1 (2)" sheetId="6" r:id="rId1"/>
+    <sheet name="FRM-EIB04" sheetId="6" r:id="rId1"/>
     <sheet name="วิธีการใช้งานแบบฟอร์ม" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'WRM1 (2)'!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'FRM-EIB04'!$1:$9</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -1455,10 +1455,10 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>434340</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2212722" cy="589777"/>
+    <xdr:ext cx="2500000" cy="238125"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="กล่องข้อความ 1"/>
@@ -1466,8 +1466,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3063240" y="1666875"/>
-          <a:ext cx="2212722" cy="589777"/>
+          <a:off x="3063240" y="1704975"/>
+          <a:ext cx="2500000" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1489,7 +1489,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" tIns="0" bIns="0" rtlCol="0" anchor="t">
           <a:spAutoFit/>
         </a:bodyPr>
         <a:lstStyle/>
@@ -1550,10 +1550,10 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>179070</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>333375</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2131802" cy="341055"/>
+    <xdr:ext cx="2450000" cy="238125"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="กล่องข้อความ 2"/>
@@ -1561,8 +1561,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="179070" y="1647825"/>
-          <a:ext cx="2131802" cy="341055"/>
+          <a:off x="179070" y="1704975"/>
+          <a:ext cx="2450000" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1584,7 +1584,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" tIns="0" bIns="0" rtlCol="0" anchor="t">
           <a:spAutoFit/>
         </a:bodyPr>
         <a:lstStyle/>
@@ -1982,7 +1982,7 @@
       <xdr:col>35</xdr:col>
       <xdr:colOff>68787</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>346075</xdr:rowOff>
+      <xdr:rowOff>150000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>39</xdr:col>
@@ -2023,7 +2023,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b"/>
         <a:lstStyle/>
         <a:p>
           <a:r>
@@ -2054,8 +2054,8 @@
       <xdr:rowOff>254002</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>582083</xdr:colOff>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>400000</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>380999</xdr:rowOff>
     </xdr:to>
@@ -2092,7 +2092,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b"/>
         <a:lstStyle/>
         <a:p>
           <a:r>

--- a/assets/frm-eib04-template.xlsx
+++ b/assets/frm-eib04-template.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\G_EIB\## Certification (ภายใน)\2026\เเผน-2026\คลังสินค้า\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\8014\Desktop\calibration-system-main\ตัวอย่าง\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F33F982-8F4E-4DF8-9DF4-EB1AEC33A7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32760" yWindow="330" windowWidth="12120" windowHeight="7680" tabRatio="599"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="FRM-EIB04" sheetId="6" r:id="rId1"/>
+    <sheet name="FRM-EIB04" sheetId="4" r:id="rId1"/>
     <sheet name="วิธีการใช้งานแบบฟอร์ม" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'FRM-EIB04'!$1:$9</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
   <si>
     <t>Equipment Calibration Plan</t>
   </si>
@@ -112,144 +113,20 @@
     <t>13. เอกสารแผนงานจะดำเนินการสแกนจัดเก็บไว้ที่ Z:\G_EIB\#2Certification (ภายใน)\2025\ACTION PLAN (ของแต่ละปี ค.ศ.)</t>
   </si>
   <si>
-    <t>BALANCE  30  kg</t>
+    <t>สอบเทียบภายนอก (External calibration)</t>
   </si>
   <si>
-    <t>WRM1BB05-WI01</t>
-  </si>
-  <si>
-    <t>B.4/2</t>
-  </si>
-  <si>
-    <t>WRM1BB07-WI01</t>
-  </si>
-  <si>
-    <t>B.7/1</t>
-  </si>
-  <si>
-    <t>WRM1BB08-WI01</t>
-  </si>
-  <si>
-    <t>B.7/2</t>
-  </si>
-  <si>
-    <t>WRM1BB09-WI01</t>
-  </si>
-  <si>
-    <t>B.8/2</t>
-  </si>
-  <si>
-    <t>BALANCE  300  kg</t>
-  </si>
-  <si>
-    <t>WRM1BB10-WI01</t>
-  </si>
-  <si>
-    <t>BALANCE  110  g</t>
-  </si>
-  <si>
-    <t>WRM1BB13-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB16-WI01</t>
-  </si>
-  <si>
-    <t>BALANCE  3200  g</t>
-  </si>
-  <si>
-    <t>WRM1BB17-WI01</t>
-  </si>
-  <si>
-    <t>BALANCE  34  kg</t>
-  </si>
-  <si>
-    <t>WRM1BB19-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB20-WI01</t>
-  </si>
-  <si>
-    <t>BALANCE  820  g</t>
-  </si>
-  <si>
-    <t>WRM1BB24-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB25-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB26-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB27-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB28-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB29-WI01</t>
-  </si>
-  <si>
-    <t>B.9/G</t>
-  </si>
-  <si>
-    <t>WRM1BB30-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB32-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB33-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB34-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB35-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB36-WI01</t>
-  </si>
-  <si>
-    <t>BALANCE  210  g</t>
-  </si>
-  <si>
-    <t>WRM1BB37-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB38-WI01</t>
-  </si>
-  <si>
-    <t>BALANCE  6200  g</t>
-  </si>
-  <si>
-    <t>WRM1BB39-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB40-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB41-WI01</t>
-  </si>
-  <si>
-    <t>BALANCE  6000  g</t>
-  </si>
-  <si>
-    <t>WRM1BB42-WI01</t>
-  </si>
-  <si>
-    <t>WRM1BB43-WI01</t>
+    <t>สอบเทียบภายใน (Internal calibration)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="187" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -309,8 +186,36 @@
       <name val="AngsanaUPC"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="CordiaUPC"/>
+      <family val="2"/>
+      <charset val="222"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="CordiaUPC"/>
+      <family val="2"/>
+      <charset val="222"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="AngsanaUPC"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="AngsanaUPC"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="CordiaUPC"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -377,8 +282,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="42">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -688,6 +599,19 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -909,7 +833,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -929,56 +853,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1013,6 +889,39 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1022,7 +931,7 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1034,7 +943,7 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1139,65 +1048,56 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="187" fontId="9" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1217,105 +1117,54 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1349,14 +1198,11 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1364,6 +1210,9 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1373,44 +1222,41 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1418,23 +1264,122 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="จุลภาค" xfId="1" builtinId="3"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1451,178 +1396,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>434340</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2500000" cy="238125"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="กล่องข้อความ 1"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3063240" y="1704975"/>
-          <a:ext cx="2500000" cy="238125"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" tIns="0" bIns="0" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buClrTx/>
-            <a:buSzTx/>
-            <a:buFontTx/>
-            <a:buNone/>
-            <a:tabLst/>
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1400" b="1">
-              <a:latin typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-              <a:cs typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-            </a:rPr>
-            <a:t>{{CHK_EXT}} สอบเทียบภายนอก </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-            </a:rPr>
-            <a:t>(External calibration)</a:t>
-          </a:r>
-          <a:endParaRPr lang="th-TH" sz="1400" b="1">
-            <a:effectLst/>
-            <a:latin typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-            <a:cs typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="th-TH" sz="1400" b="1">
-            <a:latin typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-            <a:cs typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>179070</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2450000" cy="238125"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="กล่องข้อความ 2"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="179070" y="1704975"/>
-          <a:ext cx="2450000" cy="238125"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" tIns="0" bIns="0" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1100" b="1" baseline="0"/>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1400" b="1" baseline="0">
-              <a:latin typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-              <a:cs typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-            </a:rPr>
-            <a:t>{{CHK_INT}} สอบเทียบ</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1400" b="1">
-              <a:latin typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-              <a:cs typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-            </a:rPr>
-            <a:t>ภายใน</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="1">
-              <a:latin typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-              <a:cs typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-            </a:rPr>
-            <a:t> (Internal calibration)</a:t>
-          </a:r>
-          <a:endParaRPr lang="th-TH" sz="1400" b="1">
-            <a:latin typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-            <a:cs typeface="AngsanaUPC" pitchFamily="18" charset="-34"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
@@ -1638,13 +1411,19 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="TextBox 2"/>
+        <xdr:cNvPr id="4" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3581400" y="38100"/>
-          <a:ext cx="4752975" cy="657225"/>
+          <a:ext cx="4752975" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1734,7 +1513,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="รูปภาพ 20"/>
+        <xdr:cNvPr id="2579" name="รูปภาพ 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000130A0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -1787,334 +1572,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>130171</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>28576</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>148163</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>314326</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="TextBox 10"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5111746" y="962026"/>
-          <a:ext cx="865717" cy="285750"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>{{MONTH}}</a:t>
-          </a:r>
-          <a:endParaRPr lang="th-TH">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>17992</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>303742</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="TextBox 11"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6286500" y="951442"/>
-          <a:ext cx="866775" cy="285750"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>{{YEAR}}</a:t>
-          </a:r>
-          <a:endParaRPr lang="th-TH" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>304800</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="TextBox 12"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5248275" y="1362075"/>
-          <a:ext cx="1438275" cy="257175"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>{{GROUP}}</a:t>
-          </a:r>
-          <a:endParaRPr lang="th-TH" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>68787</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>150000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>361951</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="TextBox 13"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8126937" y="1279525"/>
-          <a:ext cx="2217213" cy="396876"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>{{UNIT}}</a:t>
-          </a:r>
-          <a:endParaRPr lang="th-TH">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>402167</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>254002</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>43</xdr:col>
-      <xdr:colOff>400000</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>380999</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="TextBox 14"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10917767" y="1187452"/>
-          <a:ext cx="1437216" cy="507997"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>{{SECTION}}</a:t>
-          </a:r>
-          <a:endParaRPr lang="th-TH">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2130,7 +1587,13 @@
     <xdr:ext cx="3595687" cy="1200150"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="TextBox 21"/>
+        <xdr:cNvPr id="22" name="TextBox 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2332,7 +1795,13 @@
     <xdr:ext cx="2212722" cy="589777"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="กล่องข้อความ 1"/>
+        <xdr:cNvPr id="2" name="กล่องข้อความ 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2427,7 +1896,13 @@
     <xdr:ext cx="2131802" cy="341055"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="กล่องข้อความ 2"/>
+        <xdr:cNvPr id="3" name="กล่องข้อความ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2509,7 +1984,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="TextBox 2"/>
+        <xdr:cNvPr id="4" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2605,7 +2086,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4039" name="รูปภาพ 20"/>
+        <xdr:cNvPr id="4039" name="รูปภาพ 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C70F0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -2673,7 +2160,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="สี่เหลี่ยมผืนผ้า 5"/>
+        <xdr:cNvPr id="7" name="สี่เหลี่ยมผืนผ้า 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2732,7 +2225,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="สี่เหลี่ยมผืนผ้า 7"/>
+        <xdr:cNvPr id="8" name="สี่เหลี่ยมผืนผ้า 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2791,7 +2290,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="สี่เหลี่ยมผืนผ้า 8"/>
+        <xdr:cNvPr id="9" name="สี่เหลี่ยมผืนผ้า 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2850,7 +2355,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="สี่เหลี่ยมผืนผ้า 9"/>
+        <xdr:cNvPr id="10" name="สี่เหลี่ยมผืนผ้า 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2909,7 +2420,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="สี่เหลี่ยมผืนผ้า 10"/>
+        <xdr:cNvPr id="11" name="สี่เหลี่ยมผืนผ้า 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2968,22 +2485,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4045" name="Group 5"/>
+        <xdr:cNvPr id="4045" name="Group 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000CD0F0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13308806" y="928688"/>
-          <a:ext cx="3055144" cy="561975"/>
+          <a:off x="13439775" y="904875"/>
+          <a:ext cx="3162300" cy="561975"/>
           <a:chOff x="12792075" y="904875"/>
           <a:chExt cx="3143250" cy="561340"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="12" name="Rectangular Callout 11"/>
+          <xdr:cNvPr id="12" name="Rectangular Callout 11">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -3027,7 +2556,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="14" name="TextBox 13"/>
+          <xdr:cNvPr id="14" name="TextBox 13">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -3098,7 +2633,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="Rectangular Callout 14"/>
+        <xdr:cNvPr id="15" name="Rectangular Callout 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3152,7 +2693,13 @@
     <xdr:ext cx="3104880" cy="450380"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="TextBox 15"/>
+        <xdr:cNvPr id="16" name="TextBox 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3248,7 +2795,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="Rectangular Callout 16"/>
+        <xdr:cNvPr id="17" name="Rectangular Callout 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3302,7 +2855,13 @@
     <xdr:ext cx="3095086" cy="432811"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="TextBox 17"/>
+        <xdr:cNvPr id="18" name="TextBox 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3365,7 +2924,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="Rectangular Callout 18"/>
+        <xdr:cNvPr id="19" name="Rectangular Callout 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3422,7 +2987,13 @@
     <xdr:ext cx="3205162" cy="1001899"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="TextBox 20"/>
+        <xdr:cNvPr id="21" name="TextBox 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3569,7 +3140,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Rectangle 4"/>
+        <xdr:cNvPr id="5" name="Rectangle 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3626,7 +3203,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Rectangle 12"/>
+        <xdr:cNvPr id="13" name="Rectangle 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3680,7 +3263,13 @@
     <xdr:ext cx="3810000" cy="2552631"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="TextBox 23"/>
+        <xdr:cNvPr id="24" name="TextBox 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4438,22 +4027,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4055" name="Group 22"/>
+        <xdr:cNvPr id="4055" name="Group 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000D70F0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="114300" y="8793956"/>
-          <a:ext cx="3424238" cy="1271588"/>
+          <a:off x="114300" y="8801100"/>
+          <a:ext cx="3543300" cy="1285875"/>
           <a:chOff x="123825" y="8801099"/>
           <a:chExt cx="3533775" cy="1390651"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="27" name="Rectangular Callout 26"/>
+          <xdr:cNvPr id="27" name="Rectangular Callout 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -4500,7 +4101,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="31" name="TextBox 30"/>
+          <xdr:cNvPr id="31" name="TextBox 30">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001F000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -4589,7 +4196,13 @@
     <xdr:ext cx="4133604" cy="2381366"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="TextBox 31"/>
+        <xdr:cNvPr id="32" name="TextBox 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5164,7 +4777,13 @@
     <xdr:ext cx="3762375" cy="1895475"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="TextBox 32"/>
+        <xdr:cNvPr id="33" name="TextBox 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5448,7 +5067,13 @@
     <xdr:ext cx="4152608" cy="952500"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="TextBox 33"/>
+        <xdr:cNvPr id="34" name="TextBox 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5659,22 +5284,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4059" name="Group 16"/>
+        <xdr:cNvPr id="4059" name="Group 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000DB0F0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6057900" y="873919"/>
-          <a:ext cx="361950" cy="330994"/>
+          <a:off x="6143625" y="857250"/>
+          <a:ext cx="352425" cy="323850"/>
           <a:chOff x="5859780" y="1188720"/>
           <a:chExt cx="327660" cy="312420"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="39" name="Oval 38"/>
+          <xdr:cNvPr id="39" name="Oval 38">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000027000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -5720,7 +5357,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="40" name="TextBox 39"/>
+          <xdr:cNvPr id="40" name="TextBox 39">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000028000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -5782,22 +5425,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4060" name="Group 16"/>
+        <xdr:cNvPr id="4060" name="Group 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000DC0F0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6615113" y="1233488"/>
-          <a:ext cx="338137" cy="342900"/>
+          <a:off x="6686550" y="1209675"/>
+          <a:ext cx="333375" cy="342900"/>
           <a:chOff x="5859780" y="1188720"/>
           <a:chExt cx="327660" cy="312420"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="45" name="Oval 44"/>
+          <xdr:cNvPr id="45" name="Oval 44">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002D000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -5843,7 +5498,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="46" name="TextBox 45"/>
+          <xdr:cNvPr id="46" name="TextBox 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002E000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -5905,14 +5566,20 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4061" name="Group 16"/>
+        <xdr:cNvPr id="4061" name="Group 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000DD0F0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="9858375" y="1223963"/>
+          <a:off x="9896475" y="1200150"/>
           <a:ext cx="352425" cy="342900"/>
           <a:chOff x="5859780" y="1188720"/>
           <a:chExt cx="327660" cy="312420"/>
@@ -5920,7 +5587,13 @@
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="51" name="Oval 50"/>
+          <xdr:cNvPr id="51" name="Oval 50">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000033000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -5966,7 +5639,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="52" name="TextBox 51"/>
+          <xdr:cNvPr id="52" name="TextBox 51">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000034000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -6028,22 +5707,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4062" name="Group 16"/>
+        <xdr:cNvPr id="4062" name="Group 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000DE0F0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2386013" y="1614488"/>
-          <a:ext cx="347662" cy="347662"/>
+          <a:off x="2457450" y="1590675"/>
+          <a:ext cx="371475" cy="333375"/>
           <a:chOff x="5859780" y="1188720"/>
           <a:chExt cx="327660" cy="312420"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="54" name="Oval 53"/>
+          <xdr:cNvPr id="54" name="Oval 53">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000036000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -6089,7 +5780,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="55" name="TextBox 54"/>
+          <xdr:cNvPr id="55" name="TextBox 54">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000037000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -6151,22 +5848,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4063" name="Group 16"/>
+        <xdr:cNvPr id="4063" name="Group 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000DF0F0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="10144125" y="1595438"/>
-          <a:ext cx="347663" cy="342900"/>
+          <a:off x="10182225" y="1571625"/>
+          <a:ext cx="361950" cy="342900"/>
           <a:chOff x="5859780" y="1188720"/>
           <a:chExt cx="327660" cy="312420"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="57" name="Oval 56"/>
+          <xdr:cNvPr id="57" name="Oval 56">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000039000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -6212,7 +5921,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="58" name="TextBox 57"/>
+          <xdr:cNvPr id="58" name="TextBox 57">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00003A000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -6274,22 +5989,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4064" name="Group 16"/>
+        <xdr:cNvPr id="4064" name="Group 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000E00F0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1304925" y="3905250"/>
-          <a:ext cx="352425" cy="340519"/>
+          <a:off x="1343025" y="3876675"/>
+          <a:ext cx="352425" cy="342900"/>
           <a:chOff x="5859780" y="1188720"/>
           <a:chExt cx="327660" cy="312420"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="60" name="Oval 59"/>
+          <xdr:cNvPr id="60" name="Oval 59">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00003C000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -6335,7 +6062,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="61" name="TextBox 60"/>
+          <xdr:cNvPr id="61" name="TextBox 60">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00003D000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -6397,22 +6130,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4065" name="Group 16"/>
+        <xdr:cNvPr id="4065" name="Group 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000E10F0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5891213" y="3905250"/>
-          <a:ext cx="509587" cy="376238"/>
+          <a:off x="5981700" y="3876675"/>
+          <a:ext cx="495300" cy="381000"/>
           <a:chOff x="5859780" y="1188720"/>
           <a:chExt cx="327660" cy="312420"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="63" name="Oval 62"/>
+          <xdr:cNvPr id="63" name="Oval 62">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00003F000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -6458,7 +6203,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="64" name="TextBox 63"/>
+          <xdr:cNvPr id="64" name="TextBox 63">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000040000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -6520,22 +6271,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4066" name="Group 16"/>
+        <xdr:cNvPr id="4066" name="Group 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000E20F0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2047875" y="8117681"/>
-          <a:ext cx="347663" cy="340519"/>
+          <a:off x="2085975" y="8124825"/>
+          <a:ext cx="381000" cy="342900"/>
           <a:chOff x="5859780" y="1188720"/>
           <a:chExt cx="327660" cy="312420"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="66" name="Oval 65"/>
+          <xdr:cNvPr id="66" name="Oval 65">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000042000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -6581,7 +6344,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="67" name="TextBox 66"/>
+          <xdr:cNvPr id="67" name="TextBox 66">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000043000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -6643,22 +6412,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4067" name="Group 16"/>
+        <xdr:cNvPr id="4067" name="Group 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000E30F0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="10825163" y="4810125"/>
-          <a:ext cx="426243" cy="388144"/>
+          <a:off x="10877550" y="4791075"/>
+          <a:ext cx="447675" cy="390525"/>
           <a:chOff x="5859780" y="1188720"/>
           <a:chExt cx="327660" cy="312420"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="72" name="Oval 71"/>
+          <xdr:cNvPr id="72" name="Oval 71">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000048000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -6704,7 +6485,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="73" name="TextBox 72"/>
+          <xdr:cNvPr id="73" name="TextBox 72">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000049000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -6766,22 +6553,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4068" name="Group 16"/>
+        <xdr:cNvPr id="4068" name="Group 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000E40F0000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="12187238" y="8117681"/>
-          <a:ext cx="440531" cy="359569"/>
+          <a:off x="12287250" y="8124825"/>
+          <a:ext cx="447675" cy="361950"/>
           <a:chOff x="5859780" y="1188720"/>
           <a:chExt cx="327660" cy="312420"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="75" name="Oval 74"/>
+          <xdr:cNvPr id="75" name="Oval 74">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00004B000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -6827,7 +6626,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="76" name="TextBox 75"/>
+          <xdr:cNvPr id="76" name="TextBox 75">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00004C000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr txBox="1"/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -7134,96 +6939,114 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <tabColor rgb="FFFFC000"/>
+    <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AR9"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="19.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" style="1" customWidth="1"/>
-    <col min="6" max="14" width="2.140625" style="1" customWidth="1"/>
-    <col min="15" max="17" width="2.5703125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="2.42578125" style="1" customWidth="1"/>
-    <col min="19" max="36" width="2.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" style="1" customWidth="1"/>
+    <col min="6" max="14" width="2.109375" style="1" customWidth="1"/>
+    <col min="15" max="17" width="2.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="2.44140625" style="1" customWidth="1"/>
+    <col min="19" max="36" width="2.5546875" style="1" customWidth="1"/>
     <col min="37" max="37" width="9" style="1" customWidth="1"/>
-    <col min="38" max="38" width="7.42578125" style="1" customWidth="1"/>
-    <col min="39" max="39" width="8.42578125" style="1" customWidth="1"/>
-    <col min="40" max="43" width="9.42578125" style="1" customWidth="1"/>
-    <col min="44" max="16384" width="9.140625" style="1"/>
+    <col min="38" max="38" width="7.44140625" style="1" customWidth="1"/>
+    <col min="39" max="39" width="8.44140625" style="1" customWidth="1"/>
+    <col min="40" max="43" width="9.44140625" style="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44" ht="23.4" x14ac:dyDescent="0.25">
       <c r="AO1" s="2"/>
     </row>
-    <row r="3" spans="1:44" ht="29.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A3" s="116" t="s">
+    <row r="3" spans="1:44" ht="29.25" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="A3" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="116"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="116"/>
-      <c r="M3" s="116"/>
-      <c r="N3" s="116"/>
-      <c r="O3" s="116"/>
-      <c r="P3" s="116"/>
-      <c r="Q3" s="116"/>
-      <c r="R3" s="116"/>
-      <c r="S3" s="116"/>
-      <c r="T3" s="116"/>
-      <c r="U3" s="116"/>
-      <c r="V3" s="116"/>
-      <c r="W3" s="116"/>
-      <c r="X3" s="116"/>
-      <c r="Y3" s="116"/>
-      <c r="Z3" s="116"/>
-      <c r="AA3" s="116"/>
-      <c r="AB3" s="116"/>
-      <c r="AC3" s="116"/>
-      <c r="AD3" s="116"/>
-      <c r="AE3" s="116"/>
-      <c r="AF3" s="116"/>
-      <c r="AG3" s="116"/>
-      <c r="AH3" s="116"/>
-      <c r="AI3" s="116"/>
-      <c r="AJ3" s="116"/>
-      <c r="AK3" s="116"/>
-      <c r="AL3" s="116"/>
-      <c r="AM3" s="116"/>
-      <c r="AN3" s="116"/>
-      <c r="AO3" s="116"/>
-      <c r="AP3" s="116"/>
-      <c r="AQ3" s="116"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="102"/>
+      <c r="S3" s="102"/>
+      <c r="T3" s="102"/>
+      <c r="U3" s="102"/>
+      <c r="V3" s="102"/>
+      <c r="W3" s="102"/>
+      <c r="X3" s="102"/>
+      <c r="Y3" s="102"/>
+      <c r="Z3" s="102"/>
+      <c r="AA3" s="102"/>
+      <c r="AB3" s="102"/>
+      <c r="AC3" s="102"/>
+      <c r="AD3" s="102"/>
+      <c r="AE3" s="102"/>
+      <c r="AF3" s="102"/>
+      <c r="AG3" s="102"/>
+      <c r="AH3" s="102"/>
+      <c r="AI3" s="102"/>
+      <c r="AJ3" s="102"/>
+      <c r="AK3" s="102"/>
+      <c r="AL3" s="102"/>
+      <c r="AM3" s="102"/>
+      <c r="AN3" s="102"/>
+      <c r="AO3" s="102"/>
+      <c r="AP3" s="102"/>
+      <c r="AQ3" s="102"/>
     </row>
-    <row r="4" spans="1:44" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F4" s="2" t="s">
-        <v>15</v>
+    <row r="4" spans="1:44" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                   Month  {{MONTH}} Year {{YEAR}}</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:44" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="AE5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN5" s="2" t="s">
-        <v>22</v>
+    <row r="5" spans="1:44" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">กลุ่มเครื่องตรวจ เครื่องวัดและเครื่องทดสอบ (Inspection, measuring and testing instruments group) {{GROUP}}</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">หน่วยงาน (Unit) {{UNIT}}</t>
+        </is>
+      </c>
+      <c r="AN5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">แผนก (Section) {{SECTION}}</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:44" s="3" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" s="3" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{CHK_INT}} สอบเทียบภายใน (Internal calibration)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{CHK_EXT}} สอบเทียบภายนอก (External calibration)</t>
+        </is>
+      </c>
       <c r="F6" s="2"/>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -7241,222 +7064,222 @@
         </is>
       </c>
     </row>
-    <row r="7" spans="1:44" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="117" t="s">
+    <row r="7" spans="1:44" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="120" t="s">
+      <c r="B7" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="117" t="s">
+      <c r="C7" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="123" t="s">
+      <c r="D7" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="126" t="s">
+      <c r="E7" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="129" t="s">
+      <c r="F7" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="130"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="130"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="130"/>
-      <c r="S7" s="130"/>
-      <c r="T7" s="130"/>
-      <c r="U7" s="130"/>
-      <c r="V7" s="130"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="130"/>
-      <c r="Y7" s="130"/>
-      <c r="Z7" s="130"/>
-      <c r="AA7" s="130"/>
-      <c r="AB7" s="130"/>
-      <c r="AC7" s="130"/>
-      <c r="AD7" s="130"/>
-      <c r="AE7" s="130"/>
-      <c r="AF7" s="130"/>
-      <c r="AG7" s="130"/>
-      <c r="AH7" s="130"/>
-      <c r="AI7" s="130"/>
-      <c r="AJ7" s="131"/>
-      <c r="AK7" s="132" t="s">
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="85"/>
+      <c r="K7" s="85"/>
+      <c r="L7" s="85"/>
+      <c r="M7" s="85"/>
+      <c r="N7" s="85"/>
+      <c r="O7" s="85"/>
+      <c r="P7" s="85"/>
+      <c r="Q7" s="85"/>
+      <c r="R7" s="85"/>
+      <c r="S7" s="85"/>
+      <c r="T7" s="85"/>
+      <c r="U7" s="85"/>
+      <c r="V7" s="85"/>
+      <c r="W7" s="85"/>
+      <c r="X7" s="85"/>
+      <c r="Y7" s="85"/>
+      <c r="Z7" s="85"/>
+      <c r="AA7" s="85"/>
+      <c r="AB7" s="85"/>
+      <c r="AC7" s="85"/>
+      <c r="AD7" s="85"/>
+      <c r="AE7" s="85"/>
+      <c r="AF7" s="85"/>
+      <c r="AG7" s="85"/>
+      <c r="AH7" s="85"/>
+      <c r="AI7" s="85"/>
+      <c r="AJ7" s="86"/>
+      <c r="AK7" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="AL7" s="132"/>
-      <c r="AM7" s="132"/>
-      <c r="AN7" s="132"/>
-      <c r="AO7" s="132"/>
-      <c r="AP7" s="132"/>
-      <c r="AQ7" s="133"/>
+      <c r="AL7" s="109"/>
+      <c r="AM7" s="109"/>
+      <c r="AN7" s="109"/>
+      <c r="AO7" s="109"/>
+      <c r="AP7" s="109"/>
+      <c r="AQ7" s="110"/>
     </row>
-    <row r="8" spans="1:44" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="118"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="134">
+    <row r="8" spans="1:44" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="76"/>
+      <c r="B8" s="73"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="98">
         <v>1</v>
       </c>
-      <c r="G8" s="110">
+      <c r="G8" s="87">
         <v>2</v>
       </c>
-      <c r="H8" s="110">
+      <c r="H8" s="87">
         <v>3</v>
       </c>
-      <c r="I8" s="110">
+      <c r="I8" s="87">
         <v>4</v>
       </c>
-      <c r="J8" s="110">
+      <c r="J8" s="87">
         <v>5</v>
       </c>
-      <c r="K8" s="110">
+      <c r="K8" s="87">
         <v>6</v>
       </c>
-      <c r="L8" s="110">
+      <c r="L8" s="87">
         <v>7</v>
       </c>
-      <c r="M8" s="110">
+      <c r="M8" s="87">
         <v>8</v>
       </c>
-      <c r="N8" s="110">
+      <c r="N8" s="87">
         <v>9</v>
       </c>
-      <c r="O8" s="110">
+      <c r="O8" s="87">
         <v>10</v>
       </c>
-      <c r="P8" s="110">
+      <c r="P8" s="87">
         <v>11</v>
       </c>
-      <c r="Q8" s="110">
+      <c r="Q8" s="87">
         <v>12</v>
       </c>
-      <c r="R8" s="110">
+      <c r="R8" s="87">
         <v>13</v>
       </c>
-      <c r="S8" s="110">
+      <c r="S8" s="87">
         <v>14</v>
       </c>
-      <c r="T8" s="110">
+      <c r="T8" s="87">
         <v>15</v>
       </c>
-      <c r="U8" s="110">
+      <c r="U8" s="87">
         <v>16</v>
       </c>
-      <c r="V8" s="110">
+      <c r="V8" s="87">
         <v>17</v>
       </c>
-      <c r="W8" s="110">
+      <c r="W8" s="87">
         <v>18</v>
       </c>
-      <c r="X8" s="110">
+      <c r="X8" s="87">
         <v>19</v>
       </c>
-      <c r="Y8" s="110">
+      <c r="Y8" s="87">
         <v>20</v>
       </c>
-      <c r="Z8" s="110">
+      <c r="Z8" s="87">
         <v>21</v>
       </c>
-      <c r="AA8" s="110">
+      <c r="AA8" s="87">
         <v>22</v>
       </c>
-      <c r="AB8" s="110">
+      <c r="AB8" s="87">
         <v>23</v>
       </c>
-      <c r="AC8" s="110">
+      <c r="AC8" s="87">
         <v>24</v>
       </c>
-      <c r="AD8" s="110">
+      <c r="AD8" s="87">
         <v>25</v>
       </c>
-      <c r="AE8" s="110">
+      <c r="AE8" s="87">
         <v>26</v>
       </c>
-      <c r="AF8" s="110">
+      <c r="AF8" s="87">
         <v>27</v>
       </c>
-      <c r="AG8" s="110">
+      <c r="AG8" s="87">
         <v>28</v>
       </c>
-      <c r="AH8" s="110">
+      <c r="AH8" s="87">
         <v>29</v>
       </c>
-      <c r="AI8" s="110">
+      <c r="AI8" s="87">
         <v>30</v>
       </c>
-      <c r="AJ8" s="112">
+      <c r="AJ8" s="103">
         <v>31</v>
       </c>
-      <c r="AK8" s="114" t="s">
+      <c r="AK8" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="AL8" s="103" t="s">
+      <c r="AL8" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="AM8" s="105" t="s">
+      <c r="AM8" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="AN8" s="107" t="s">
+      <c r="AN8" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="AO8" s="108"/>
-      <c r="AP8" s="107" t="s">
+      <c r="AO8" s="96"/>
+      <c r="AP8" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="109"/>
+      <c r="AQ8" s="97"/>
     </row>
-    <row r="9" spans="1:44" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="119"/>
-      <c r="B9" s="122"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="128"/>
-      <c r="F9" s="135"/>
-      <c r="G9" s="111"/>
-      <c r="H9" s="111"/>
-      <c r="I9" s="111"/>
-      <c r="J9" s="111"/>
-      <c r="K9" s="111"/>
-      <c r="L9" s="111"/>
-      <c r="M9" s="111"/>
-      <c r="N9" s="111"/>
-      <c r="O9" s="111"/>
-      <c r="P9" s="111"/>
-      <c r="Q9" s="111"/>
-      <c r="R9" s="111"/>
-      <c r="S9" s="111"/>
-      <c r="T9" s="111"/>
-      <c r="U9" s="111"/>
-      <c r="V9" s="111"/>
-      <c r="W9" s="111"/>
-      <c r="X9" s="111"/>
-      <c r="Y9" s="111"/>
-      <c r="Z9" s="111"/>
-      <c r="AA9" s="111"/>
-      <c r="AB9" s="111"/>
-      <c r="AC9" s="111"/>
-      <c r="AD9" s="111"/>
-      <c r="AE9" s="111"/>
-      <c r="AF9" s="111"/>
-      <c r="AG9" s="111"/>
-      <c r="AH9" s="111"/>
-      <c r="AI9" s="111"/>
-      <c r="AJ9" s="113"/>
-      <c r="AK9" s="115"/>
-      <c r="AL9" s="104"/>
-      <c r="AM9" s="106"/>
+    <row r="9" spans="1:44" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="77"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="88"/>
+      <c r="J9" s="88"/>
+      <c r="K9" s="88"/>
+      <c r="L9" s="88"/>
+      <c r="M9" s="88"/>
+      <c r="N9" s="88"/>
+      <c r="O9" s="88"/>
+      <c r="P9" s="88"/>
+      <c r="Q9" s="88"/>
+      <c r="R9" s="88"/>
+      <c r="S9" s="88"/>
+      <c r="T9" s="88"/>
+      <c r="U9" s="88"/>
+      <c r="V9" s="88"/>
+      <c r="W9" s="88"/>
+      <c r="X9" s="88"/>
+      <c r="Y9" s="88"/>
+      <c r="Z9" s="88"/>
+      <c r="AA9" s="88"/>
+      <c r="AB9" s="88"/>
+      <c r="AC9" s="88"/>
+      <c r="AD9" s="88"/>
+      <c r="AE9" s="88"/>
+      <c r="AF9" s="88"/>
+      <c r="AG9" s="88"/>
+      <c r="AH9" s="88"/>
+      <c r="AI9" s="88"/>
+      <c r="AJ9" s="104"/>
+      <c r="AK9" s="106"/>
+      <c r="AL9" s="108"/>
+      <c r="AM9" s="101"/>
       <c r="AN9" s="4" t="s">
         <v>12</v>
       </c>
@@ -7473,52 +7296,52 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="AM8:AM9"/>
     <mergeCell ref="A3:AQ3"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:AJ7"/>
-    <mergeCell ref="AK7:AQ7"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="AN8:AO8"/>
-    <mergeCell ref="AP8:AQ8"/>
     <mergeCell ref="AF8:AF9"/>
     <mergeCell ref="AG8:AG9"/>
     <mergeCell ref="AH8:AH9"/>
     <mergeCell ref="AI8:AI9"/>
     <mergeCell ref="AJ8:AJ9"/>
     <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AK7:AQ7"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="AN8:AO8"/>
+    <mergeCell ref="AP8:AQ8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:AJ7"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="T8:T9"/>
   </mergeCells>
-  <pageMargins left="0.27559055118110237" right="0.23622047244094491" top="0" bottom="0.38" header="0" footer="0"/>
+  <pageMargins left="0.27559055118110237" right="0.23622047244094491" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="77" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L&amp;"AngsanaUPC,Regular"&amp;14FRM-EIB04 (TP) Rev.03&amp;C&amp;"AngsanaUPC,Regular"&amp;14Effective Date: 31/03/2025 (5Y)&amp;R&amp;"AngsanaUPC,Regular"&amp;14Page &amp;P of &amp;N</oddFooter>
@@ -7528,1368 +7351,1368 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AR41"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="19.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" style="1" customWidth="1"/>
-    <col min="6" max="14" width="2.140625" style="1" customWidth="1"/>
-    <col min="15" max="36" width="3.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" style="1" customWidth="1"/>
+    <col min="6" max="14" width="2.109375" style="1" customWidth="1"/>
+    <col min="15" max="36" width="3.109375" style="1" customWidth="1"/>
     <col min="37" max="37" width="9" style="1" customWidth="1"/>
-    <col min="38" max="38" width="7.42578125" style="1" customWidth="1"/>
-    <col min="39" max="39" width="8.42578125" style="1" customWidth="1"/>
+    <col min="38" max="38" width="7.44140625" style="1" customWidth="1"/>
+    <col min="39" max="39" width="8.44140625" style="1" customWidth="1"/>
     <col min="40" max="40" width="7" style="1" customWidth="1"/>
-    <col min="41" max="41" width="8.85546875" style="1" customWidth="1"/>
-    <col min="42" max="42" width="6.5703125" style="1" customWidth="1"/>
-    <col min="43" max="43" width="8.28515625" style="1" customWidth="1"/>
-    <col min="44" max="16384" width="9.140625" style="1"/>
+    <col min="41" max="41" width="8.88671875" style="1" customWidth="1"/>
+    <col min="42" max="42" width="6.5546875" style="1" customWidth="1"/>
+    <col min="43" max="43" width="8.33203125" style="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="23.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44" ht="23.4" x14ac:dyDescent="0.25">
       <c r="AO1" s="2"/>
     </row>
-    <row r="3" spans="1:44" ht="29.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A3" s="116" t="s">
+    <row r="3" spans="1:44" ht="29.25" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="A3" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="116"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="116"/>
-      <c r="M3" s="116"/>
-      <c r="N3" s="116"/>
-      <c r="O3" s="116"/>
-      <c r="P3" s="116"/>
-      <c r="Q3" s="116"/>
-      <c r="R3" s="116"/>
-      <c r="S3" s="116"/>
-      <c r="T3" s="116"/>
-      <c r="U3" s="116"/>
-      <c r="V3" s="116"/>
-      <c r="W3" s="116"/>
-      <c r="X3" s="116"/>
-      <c r="Y3" s="116"/>
-      <c r="Z3" s="116"/>
-      <c r="AA3" s="116"/>
-      <c r="AB3" s="116"/>
-      <c r="AC3" s="116"/>
-      <c r="AD3" s="116"/>
-      <c r="AE3" s="116"/>
-      <c r="AF3" s="116"/>
-      <c r="AG3" s="116"/>
-      <c r="AH3" s="116"/>
-      <c r="AI3" s="116"/>
-      <c r="AJ3" s="116"/>
-      <c r="AK3" s="116"/>
-      <c r="AL3" s="116"/>
-      <c r="AM3" s="116"/>
-      <c r="AN3" s="116"/>
-      <c r="AO3" s="116"/>
-      <c r="AP3" s="116"/>
-      <c r="AQ3" s="116"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="102"/>
+      <c r="S3" s="102"/>
+      <c r="T3" s="102"/>
+      <c r="U3" s="102"/>
+      <c r="V3" s="102"/>
+      <c r="W3" s="102"/>
+      <c r="X3" s="102"/>
+      <c r="Y3" s="102"/>
+      <c r="Z3" s="102"/>
+      <c r="AA3" s="102"/>
+      <c r="AB3" s="102"/>
+      <c r="AC3" s="102"/>
+      <c r="AD3" s="102"/>
+      <c r="AE3" s="102"/>
+      <c r="AF3" s="102"/>
+      <c r="AG3" s="102"/>
+      <c r="AH3" s="102"/>
+      <c r="AI3" s="102"/>
+      <c r="AJ3" s="102"/>
+      <c r="AK3" s="102"/>
+      <c r="AL3" s="102"/>
+      <c r="AM3" s="102"/>
+      <c r="AN3" s="102"/>
+      <c r="AO3" s="102"/>
+      <c r="AP3" s="102"/>
+      <c r="AQ3" s="102"/>
     </row>
-    <row r="4" spans="1:44" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:44" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="32"/>
-      <c r="R4" s="32"/>
-      <c r="S4" s="32"/>
-      <c r="T4" s="32"/>
-      <c r="U4" s="32"/>
-      <c r="V4" s="32"/>
-      <c r="W4" s="32"/>
-      <c r="X4" s="32"/>
-      <c r="Y4" s="32"/>
-      <c r="Z4" s="32"/>
-      <c r="AA4" s="32"/>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="32"/>
-      <c r="AD4" s="32"/>
-      <c r="AE4" s="32"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="16"/>
+      <c r="AA4" s="16"/>
+      <c r="AB4" s="16"/>
+      <c r="AC4" s="16"/>
+      <c r="AD4" s="16"/>
+      <c r="AE4" s="16"/>
     </row>
-    <row r="5" spans="1:44" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="33" t="s">
+    <row r="5" spans="1:44" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
-      <c r="S5" s="33"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="33"/>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33"/>
-      <c r="Y5" s="33"/>
-      <c r="Z5" s="33"/>
-      <c r="AA5" s="33"/>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="33"/>
-      <c r="AD5" s="33"/>
-      <c r="AE5" s="34" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="17"/>
+      <c r="AA5" s="17"/>
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="17"/>
+      <c r="AD5" s="17"/>
+      <c r="AE5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="AF5" s="34"/>
-      <c r="AG5" s="34"/>
-      <c r="AH5" s="34"/>
-      <c r="AI5" s="34"/>
-      <c r="AJ5" s="34"/>
-      <c r="AK5" s="34"/>
-      <c r="AL5" s="34"/>
-      <c r="AM5" s="34"/>
-      <c r="AN5" s="34" t="s">
+      <c r="AF5" s="18"/>
+      <c r="AG5" s="18"/>
+      <c r="AH5" s="18"/>
+      <c r="AI5" s="18"/>
+      <c r="AJ5" s="18"/>
+      <c r="AK5" s="18"/>
+      <c r="AL5" s="18"/>
+      <c r="AM5" s="18"/>
+      <c r="AN5" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="AO5" s="34"/>
-      <c r="AP5" s="34"/>
-      <c r="AQ5" s="34"/>
+      <c r="AO5" s="18"/>
+      <c r="AP5" s="18"/>
+      <c r="AQ5" s="18"/>
     </row>
-    <row r="6" spans="1:44" s="3" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="35"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="37"/>
-      <c r="V6" s="37"/>
-      <c r="W6" s="37"/>
-      <c r="X6" s="37"/>
-      <c r="Y6" s="37"/>
-      <c r="Z6" s="37" t="s">
+    <row r="6" spans="1:44" s="3" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="30"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="32"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="AA6" s="37"/>
-      <c r="AB6" s="37"/>
-      <c r="AC6" s="37"/>
-      <c r="AD6" s="37"/>
-      <c r="AE6" s="37"/>
-      <c r="AF6" s="37"/>
-      <c r="AG6" s="37"/>
-      <c r="AH6" s="37"/>
-      <c r="AI6" s="37" t="s">
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="32"/>
+      <c r="AE6" s="32"/>
+      <c r="AF6" s="32"/>
+      <c r="AG6" s="32"/>
+      <c r="AH6" s="32"/>
+      <c r="AI6" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="AJ6" s="37"/>
-      <c r="AK6" s="37"/>
-      <c r="AL6" s="37"/>
-      <c r="AM6" s="37"/>
-      <c r="AN6" s="37" t="s">
+      <c r="AJ6" s="32"/>
+      <c r="AK6" s="32"/>
+      <c r="AL6" s="32"/>
+      <c r="AM6" s="32"/>
+      <c r="AN6" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="AO6" s="37"/>
-      <c r="AP6" s="37"/>
-      <c r="AQ6" s="37"/>
+      <c r="AO6" s="32"/>
+      <c r="AP6" s="32"/>
+      <c r="AQ6" s="32"/>
     </row>
-    <row r="7" spans="1:44" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="155" t="s">
+    <row r="7" spans="1:44" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="158" t="s">
+      <c r="B7" s="133" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="155" t="s">
+      <c r="C7" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="161" t="s">
+      <c r="D7" s="136" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="164" t="s">
+      <c r="E7" s="139" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="167" t="s">
+      <c r="F7" s="142" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="168"/>
-      <c r="H7" s="168"/>
-      <c r="I7" s="168"/>
-      <c r="J7" s="168"/>
-      <c r="K7" s="168"/>
-      <c r="L7" s="168"/>
-      <c r="M7" s="168"/>
-      <c r="N7" s="168"/>
-      <c r="O7" s="168"/>
-      <c r="P7" s="168"/>
-      <c r="Q7" s="168"/>
-      <c r="R7" s="168"/>
-      <c r="S7" s="168"/>
-      <c r="T7" s="168"/>
-      <c r="U7" s="168"/>
-      <c r="V7" s="168"/>
-      <c r="W7" s="168"/>
-      <c r="X7" s="168"/>
-      <c r="Y7" s="168"/>
-      <c r="Z7" s="168"/>
-      <c r="AA7" s="168"/>
-      <c r="AB7" s="168"/>
-      <c r="AC7" s="168"/>
-      <c r="AD7" s="168"/>
-      <c r="AE7" s="168"/>
-      <c r="AF7" s="168"/>
-      <c r="AG7" s="168"/>
-      <c r="AH7" s="168"/>
-      <c r="AI7" s="168"/>
-      <c r="AJ7" s="169"/>
-      <c r="AK7" s="170" t="s">
+      <c r="G7" s="143"/>
+      <c r="H7" s="143"/>
+      <c r="I7" s="143"/>
+      <c r="J7" s="143"/>
+      <c r="K7" s="143"/>
+      <c r="L7" s="143"/>
+      <c r="M7" s="143"/>
+      <c r="N7" s="143"/>
+      <c r="O7" s="143"/>
+      <c r="P7" s="143"/>
+      <c r="Q7" s="143"/>
+      <c r="R7" s="143"/>
+      <c r="S7" s="143"/>
+      <c r="T7" s="143"/>
+      <c r="U7" s="143"/>
+      <c r="V7" s="143"/>
+      <c r="W7" s="143"/>
+      <c r="X7" s="143"/>
+      <c r="Y7" s="143"/>
+      <c r="Z7" s="143"/>
+      <c r="AA7" s="143"/>
+      <c r="AB7" s="143"/>
+      <c r="AC7" s="143"/>
+      <c r="AD7" s="143"/>
+      <c r="AE7" s="143"/>
+      <c r="AF7" s="143"/>
+      <c r="AG7" s="143"/>
+      <c r="AH7" s="143"/>
+      <c r="AI7" s="143"/>
+      <c r="AJ7" s="144"/>
+      <c r="AK7" s="145" t="s">
         <v>23</v>
       </c>
-      <c r="AL7" s="170"/>
-      <c r="AM7" s="170"/>
-      <c r="AN7" s="170"/>
-      <c r="AO7" s="170"/>
-      <c r="AP7" s="170"/>
-      <c r="AQ7" s="171"/>
+      <c r="AL7" s="145"/>
+      <c r="AM7" s="145"/>
+      <c r="AN7" s="145"/>
+      <c r="AO7" s="145"/>
+      <c r="AP7" s="145"/>
+      <c r="AQ7" s="146"/>
     </row>
-    <row r="8" spans="1:44" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="156"/>
-      <c r="B8" s="159"/>
-      <c r="C8" s="156"/>
-      <c r="D8" s="162"/>
-      <c r="E8" s="165"/>
-      <c r="F8" s="172">
+    <row r="8" spans="1:44" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="131"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="131"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="140"/>
+      <c r="F8" s="147">
         <v>1</v>
       </c>
-      <c r="G8" s="139">
+      <c r="G8" s="114">
         <v>2</v>
       </c>
-      <c r="H8" s="139">
+      <c r="H8" s="114">
         <v>3</v>
       </c>
-      <c r="I8" s="139">
+      <c r="I8" s="114">
         <v>4</v>
       </c>
-      <c r="J8" s="139">
+      <c r="J8" s="114">
         <v>5</v>
       </c>
-      <c r="K8" s="139">
+      <c r="K8" s="114">
         <v>6</v>
       </c>
-      <c r="L8" s="139">
+      <c r="L8" s="114">
         <v>7</v>
       </c>
-      <c r="M8" s="139">
+      <c r="M8" s="114">
         <v>8</v>
       </c>
-      <c r="N8" s="139">
+      <c r="N8" s="114">
         <v>9</v>
       </c>
-      <c r="O8" s="139">
+      <c r="O8" s="114">
         <v>10</v>
       </c>
-      <c r="P8" s="139">
+      <c r="P8" s="114">
         <v>11</v>
       </c>
-      <c r="Q8" s="139">
+      <c r="Q8" s="114">
         <v>12</v>
       </c>
-      <c r="R8" s="139">
+      <c r="R8" s="114">
         <v>13</v>
       </c>
-      <c r="S8" s="139">
+      <c r="S8" s="114">
         <v>14</v>
       </c>
-      <c r="T8" s="139">
+      <c r="T8" s="114">
         <v>15</v>
       </c>
-      <c r="U8" s="139">
+      <c r="U8" s="114">
         <v>16</v>
       </c>
-      <c r="V8" s="139">
+      <c r="V8" s="114">
         <v>17</v>
       </c>
-      <c r="W8" s="139">
+      <c r="W8" s="114">
         <v>18</v>
       </c>
-      <c r="X8" s="139">
+      <c r="X8" s="114">
         <v>19</v>
       </c>
-      <c r="Y8" s="139">
+      <c r="Y8" s="114">
         <v>20</v>
       </c>
-      <c r="Z8" s="139">
+      <c r="Z8" s="114">
         <v>21</v>
       </c>
-      <c r="AA8" s="139">
+      <c r="AA8" s="114">
         <v>22</v>
       </c>
-      <c r="AB8" s="139">
+      <c r="AB8" s="114">
         <v>23</v>
       </c>
-      <c r="AC8" s="139">
+      <c r="AC8" s="114">
         <v>24</v>
       </c>
-      <c r="AD8" s="139">
+      <c r="AD8" s="114">
         <v>25</v>
       </c>
-      <c r="AE8" s="139">
+      <c r="AE8" s="114">
         <v>26</v>
       </c>
-      <c r="AF8" s="139">
+      <c r="AF8" s="114">
         <v>27</v>
       </c>
-      <c r="AG8" s="139">
+      <c r="AG8" s="114">
         <v>28</v>
       </c>
-      <c r="AH8" s="139">
+      <c r="AH8" s="114">
         <v>29</v>
       </c>
-      <c r="AI8" s="139">
+      <c r="AI8" s="114">
         <v>30</v>
       </c>
-      <c r="AJ8" s="141">
+      <c r="AJ8" s="116">
         <v>31</v>
       </c>
-      <c r="AK8" s="143" t="s">
+      <c r="AK8" s="118" t="s">
         <v>14</v>
       </c>
-      <c r="AL8" s="145" t="s">
+      <c r="AL8" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="AM8" s="147" t="s">
+      <c r="AM8" s="122" t="s">
         <v>9</v>
       </c>
-      <c r="AN8" s="149" t="s">
+      <c r="AN8" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="AO8" s="150"/>
-      <c r="AP8" s="149" t="s">
+      <c r="AO8" s="125"/>
+      <c r="AP8" s="124" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="151"/>
+      <c r="AQ8" s="126"/>
     </row>
-    <row r="9" spans="1:44" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="157"/>
-      <c r="B9" s="160"/>
-      <c r="C9" s="157"/>
-      <c r="D9" s="163"/>
-      <c r="E9" s="166"/>
-      <c r="F9" s="173"/>
-      <c r="G9" s="140"/>
-      <c r="H9" s="140"/>
-      <c r="I9" s="140"/>
-      <c r="J9" s="140"/>
-      <c r="K9" s="140"/>
-      <c r="L9" s="140"/>
-      <c r="M9" s="140"/>
-      <c r="N9" s="140"/>
-      <c r="O9" s="140"/>
-      <c r="P9" s="140"/>
-      <c r="Q9" s="140"/>
-      <c r="R9" s="140"/>
-      <c r="S9" s="140"/>
-      <c r="T9" s="140"/>
-      <c r="U9" s="140"/>
-      <c r="V9" s="140"/>
-      <c r="W9" s="140"/>
-      <c r="X9" s="140"/>
-      <c r="Y9" s="140"/>
-      <c r="Z9" s="140"/>
-      <c r="AA9" s="140"/>
-      <c r="AB9" s="140"/>
-      <c r="AC9" s="140"/>
-      <c r="AD9" s="140"/>
-      <c r="AE9" s="140"/>
-      <c r="AF9" s="140"/>
-      <c r="AG9" s="140"/>
-      <c r="AH9" s="140"/>
-      <c r="AI9" s="140"/>
-      <c r="AJ9" s="142"/>
-      <c r="AK9" s="144"/>
-      <c r="AL9" s="146"/>
-      <c r="AM9" s="148"/>
-      <c r="AN9" s="52" t="s">
+    <row r="9" spans="1:44" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="132"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="132"/>
+      <c r="D9" s="138"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="148"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="115"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="115"/>
+      <c r="L9" s="115"/>
+      <c r="M9" s="115"/>
+      <c r="N9" s="115"/>
+      <c r="O9" s="115"/>
+      <c r="P9" s="115"/>
+      <c r="Q9" s="115"/>
+      <c r="R9" s="115"/>
+      <c r="S9" s="115"/>
+      <c r="T9" s="115"/>
+      <c r="U9" s="115"/>
+      <c r="V9" s="115"/>
+      <c r="W9" s="115"/>
+      <c r="X9" s="115"/>
+      <c r="Y9" s="115"/>
+      <c r="Z9" s="115"/>
+      <c r="AA9" s="115"/>
+      <c r="AB9" s="115"/>
+      <c r="AC9" s="115"/>
+      <c r="AD9" s="115"/>
+      <c r="AE9" s="115"/>
+      <c r="AF9" s="115"/>
+      <c r="AG9" s="115"/>
+      <c r="AH9" s="115"/>
+      <c r="AI9" s="115"/>
+      <c r="AJ9" s="117"/>
+      <c r="AK9" s="119"/>
+      <c r="AL9" s="121"/>
+      <c r="AM9" s="123"/>
+      <c r="AN9" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="AO9" s="53" t="s">
+      <c r="AO9" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AP9" s="52" t="s">
+      <c r="AP9" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="AQ9" s="54" t="s">
+      <c r="AQ9" s="49" t="s">
         <v>4</v>
       </c>
       <c r="AR9" s="7"/>
     </row>
-    <row r="10" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="38"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="44"/>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="44"/>
-      <c r="R10" s="44"/>
-      <c r="S10" s="44"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44"/>
-      <c r="V10" s="44"/>
-      <c r="W10" s="44"/>
-      <c r="X10" s="44"/>
-      <c r="Y10" s="44"/>
-      <c r="Z10" s="44"/>
-      <c r="AA10" s="44"/>
-      <c r="AB10" s="44"/>
-      <c r="AC10" s="44"/>
-      <c r="AD10" s="44"/>
-      <c r="AE10" s="44"/>
-      <c r="AF10" s="44"/>
-      <c r="AG10" s="44"/>
-      <c r="AH10" s="44"/>
-      <c r="AI10" s="44"/>
-      <c r="AJ10" s="45"/>
-      <c r="AK10" s="55"/>
-      <c r="AL10" s="56"/>
-      <c r="AM10" s="57"/>
-      <c r="AN10" s="58"/>
-      <c r="AO10" s="58"/>
-      <c r="AP10" s="57"/>
-      <c r="AQ10" s="59"/>
+    <row r="10" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="33"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="39"/>
+      <c r="R10" s="39"/>
+      <c r="S10" s="39"/>
+      <c r="T10" s="39"/>
+      <c r="U10" s="39"/>
+      <c r="V10" s="39"/>
+      <c r="W10" s="39"/>
+      <c r="X10" s="39"/>
+      <c r="Y10" s="39"/>
+      <c r="Z10" s="39"/>
+      <c r="AA10" s="39"/>
+      <c r="AB10" s="39"/>
+      <c r="AC10" s="39"/>
+      <c r="AD10" s="39"/>
+      <c r="AE10" s="39"/>
+      <c r="AF10" s="39"/>
+      <c r="AG10" s="39"/>
+      <c r="AH10" s="39"/>
+      <c r="AI10" s="39"/>
+      <c r="AJ10" s="40"/>
+      <c r="AK10" s="50"/>
+      <c r="AL10" s="51"/>
+      <c r="AM10" s="52"/>
+      <c r="AN10" s="53"/>
+      <c r="AO10" s="53"/>
+      <c r="AP10" s="52"/>
+      <c r="AQ10" s="54"/>
     </row>
-    <row r="11" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="39"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="47"/>
-      <c r="O11" s="47"/>
-      <c r="P11" s="47"/>
-      <c r="Q11" s="47"/>
-      <c r="R11" s="47"/>
-      <c r="S11" s="47"/>
-      <c r="T11" s="47"/>
-      <c r="U11" s="47"/>
-      <c r="V11" s="47"/>
-      <c r="W11" s="47"/>
-      <c r="X11" s="47"/>
-      <c r="Y11" s="47"/>
-      <c r="Z11" s="47"/>
-      <c r="AA11" s="47"/>
-      <c r="AB11" s="47"/>
-      <c r="AC11" s="47"/>
-      <c r="AD11" s="47"/>
-      <c r="AE11" s="47"/>
-      <c r="AF11" s="47"/>
-      <c r="AG11" s="47"/>
-      <c r="AH11" s="47"/>
-      <c r="AI11" s="47"/>
-      <c r="AJ11" s="48"/>
-      <c r="AK11" s="60"/>
-      <c r="AL11" s="61"/>
-      <c r="AM11" s="62"/>
-      <c r="AN11" s="63"/>
-      <c r="AO11" s="63"/>
-      <c r="AP11" s="62"/>
-      <c r="AQ11" s="64"/>
+    <row r="11" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="34"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42"/>
+      <c r="T11" s="42"/>
+      <c r="U11" s="42"/>
+      <c r="V11" s="42"/>
+      <c r="W11" s="42"/>
+      <c r="X11" s="42"/>
+      <c r="Y11" s="42"/>
+      <c r="Z11" s="42"/>
+      <c r="AA11" s="42"/>
+      <c r="AB11" s="42"/>
+      <c r="AC11" s="42"/>
+      <c r="AD11" s="42"/>
+      <c r="AE11" s="42"/>
+      <c r="AF11" s="42"/>
+      <c r="AG11" s="42"/>
+      <c r="AH11" s="42"/>
+      <c r="AI11" s="42"/>
+      <c r="AJ11" s="43"/>
+      <c r="AK11" s="55"/>
+      <c r="AL11" s="56"/>
+      <c r="AM11" s="57"/>
+      <c r="AN11" s="58"/>
+      <c r="AO11" s="58"/>
+      <c r="AP11" s="57"/>
+      <c r="AQ11" s="59"/>
     </row>
-    <row r="12" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="39"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="47"/>
-      <c r="T12" s="47"/>
-      <c r="U12" s="47"/>
-      <c r="V12" s="47"/>
-      <c r="W12" s="47"/>
-      <c r="X12" s="47"/>
-      <c r="Y12" s="47"/>
-      <c r="Z12" s="47"/>
-      <c r="AA12" s="47"/>
-      <c r="AB12" s="47"/>
-      <c r="AC12" s="47"/>
-      <c r="AD12" s="47"/>
-      <c r="AE12" s="47"/>
-      <c r="AF12" s="47"/>
-      <c r="AG12" s="47"/>
-      <c r="AH12" s="47"/>
-      <c r="AI12" s="47"/>
-      <c r="AJ12" s="48"/>
-      <c r="AK12" s="60"/>
-      <c r="AL12" s="61"/>
-      <c r="AM12" s="62"/>
-      <c r="AN12" s="63"/>
-      <c r="AO12" s="63"/>
-      <c r="AP12" s="62"/>
-      <c r="AQ12" s="64"/>
+    <row r="12" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="34"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
+      <c r="S12" s="42"/>
+      <c r="T12" s="42"/>
+      <c r="U12" s="42"/>
+      <c r="V12" s="42"/>
+      <c r="W12" s="42"/>
+      <c r="X12" s="42"/>
+      <c r="Y12" s="42"/>
+      <c r="Z12" s="42"/>
+      <c r="AA12" s="42"/>
+      <c r="AB12" s="42"/>
+      <c r="AC12" s="42"/>
+      <c r="AD12" s="42"/>
+      <c r="AE12" s="42"/>
+      <c r="AF12" s="42"/>
+      <c r="AG12" s="42"/>
+      <c r="AH12" s="42"/>
+      <c r="AI12" s="42"/>
+      <c r="AJ12" s="43"/>
+      <c r="AK12" s="55"/>
+      <c r="AL12" s="56"/>
+      <c r="AM12" s="57"/>
+      <c r="AN12" s="58"/>
+      <c r="AO12" s="58"/>
+      <c r="AP12" s="57"/>
+      <c r="AQ12" s="59"/>
     </row>
-    <row r="13" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="39"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="47"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="47"/>
-      <c r="S13" s="47"/>
-      <c r="T13" s="47"/>
-      <c r="U13" s="47"/>
-      <c r="V13" s="47"/>
-      <c r="W13" s="47"/>
-      <c r="X13" s="47"/>
-      <c r="Y13" s="47"/>
-      <c r="Z13" s="47"/>
-      <c r="AA13" s="47"/>
-      <c r="AB13" s="47"/>
-      <c r="AC13" s="47"/>
-      <c r="AD13" s="47"/>
-      <c r="AE13" s="47"/>
-      <c r="AF13" s="47"/>
-      <c r="AG13" s="47"/>
-      <c r="AH13" s="47"/>
-      <c r="AI13" s="47"/>
-      <c r="AJ13" s="48"/>
-      <c r="AK13" s="60"/>
-      <c r="AL13" s="61"/>
-      <c r="AM13" s="62"/>
-      <c r="AN13" s="63"/>
-      <c r="AO13" s="63"/>
-      <c r="AP13" s="62"/>
-      <c r="AQ13" s="64"/>
+    <row r="13" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="42"/>
+      <c r="U13" s="42"/>
+      <c r="V13" s="42"/>
+      <c r="W13" s="42"/>
+      <c r="X13" s="42"/>
+      <c r="Y13" s="42"/>
+      <c r="Z13" s="42"/>
+      <c r="AA13" s="42"/>
+      <c r="AB13" s="42"/>
+      <c r="AC13" s="42"/>
+      <c r="AD13" s="42"/>
+      <c r="AE13" s="42"/>
+      <c r="AF13" s="42"/>
+      <c r="AG13" s="42"/>
+      <c r="AH13" s="42"/>
+      <c r="AI13" s="42"/>
+      <c r="AJ13" s="43"/>
+      <c r="AK13" s="55"/>
+      <c r="AL13" s="56"/>
+      <c r="AM13" s="57"/>
+      <c r="AN13" s="58"/>
+      <c r="AO13" s="58"/>
+      <c r="AP13" s="57"/>
+      <c r="AQ13" s="59"/>
     </row>
-    <row r="14" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="40"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="47"/>
-      <c r="T14" s="47"/>
-      <c r="U14" s="47"/>
-      <c r="V14" s="47"/>
-      <c r="W14" s="47"/>
-      <c r="X14" s="47"/>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="47"/>
-      <c r="AA14" s="47"/>
-      <c r="AB14" s="47"/>
-      <c r="AC14" s="47"/>
-      <c r="AD14" s="47"/>
-      <c r="AE14" s="47"/>
-      <c r="AF14" s="47"/>
-      <c r="AG14" s="47"/>
-      <c r="AH14" s="47"/>
-      <c r="AI14" s="47"/>
-      <c r="AJ14" s="48"/>
-      <c r="AK14" s="60"/>
-      <c r="AL14" s="61"/>
-      <c r="AM14" s="62"/>
-      <c r="AN14" s="63"/>
-      <c r="AO14" s="63"/>
-      <c r="AP14" s="62"/>
-      <c r="AQ14" s="64"/>
+    <row r="14" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="35"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="42"/>
+      <c r="T14" s="42"/>
+      <c r="U14" s="42"/>
+      <c r="V14" s="42"/>
+      <c r="W14" s="42"/>
+      <c r="X14" s="42"/>
+      <c r="Y14" s="42"/>
+      <c r="Z14" s="42"/>
+      <c r="AA14" s="42"/>
+      <c r="AB14" s="42"/>
+      <c r="AC14" s="42"/>
+      <c r="AD14" s="42"/>
+      <c r="AE14" s="42"/>
+      <c r="AF14" s="42"/>
+      <c r="AG14" s="42"/>
+      <c r="AH14" s="42"/>
+      <c r="AI14" s="42"/>
+      <c r="AJ14" s="43"/>
+      <c r="AK14" s="55"/>
+      <c r="AL14" s="56"/>
+      <c r="AM14" s="57"/>
+      <c r="AN14" s="58"/>
+      <c r="AO14" s="58"/>
+      <c r="AP14" s="57"/>
+      <c r="AQ14" s="59"/>
     </row>
-    <row r="15" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="40"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="47"/>
-      <c r="T15" s="47"/>
-      <c r="U15" s="47"/>
-      <c r="V15" s="47"/>
-      <c r="W15" s="47"/>
-      <c r="X15" s="47"/>
-      <c r="Y15" s="47"/>
-      <c r="Z15" s="47"/>
-      <c r="AA15" s="47"/>
-      <c r="AB15" s="47"/>
-      <c r="AC15" s="47"/>
-      <c r="AD15" s="47"/>
-      <c r="AE15" s="47"/>
-      <c r="AF15" s="47"/>
-      <c r="AG15" s="47"/>
-      <c r="AH15" s="47"/>
-      <c r="AI15" s="47"/>
-      <c r="AJ15" s="48"/>
-      <c r="AK15" s="60"/>
-      <c r="AL15" s="61"/>
-      <c r="AM15" s="62"/>
-      <c r="AN15" s="63"/>
-      <c r="AO15" s="63"/>
-      <c r="AP15" s="62"/>
-      <c r="AQ15" s="64"/>
+    <row r="15" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="42"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="42"/>
+      <c r="T15" s="42"/>
+      <c r="U15" s="42"/>
+      <c r="V15" s="42"/>
+      <c r="W15" s="42"/>
+      <c r="X15" s="42"/>
+      <c r="Y15" s="42"/>
+      <c r="Z15" s="42"/>
+      <c r="AA15" s="42"/>
+      <c r="AB15" s="42"/>
+      <c r="AC15" s="42"/>
+      <c r="AD15" s="42"/>
+      <c r="AE15" s="42"/>
+      <c r="AF15" s="42"/>
+      <c r="AG15" s="42"/>
+      <c r="AH15" s="42"/>
+      <c r="AI15" s="42"/>
+      <c r="AJ15" s="43"/>
+      <c r="AK15" s="55"/>
+      <c r="AL15" s="56"/>
+      <c r="AM15" s="57"/>
+      <c r="AN15" s="58"/>
+      <c r="AO15" s="58"/>
+      <c r="AP15" s="57"/>
+      <c r="AQ15" s="59"/>
     </row>
-    <row r="16" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="40"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="47"/>
-      <c r="L16" s="47"/>
-      <c r="M16" s="47"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="47"/>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="47"/>
-      <c r="S16" s="47"/>
-      <c r="T16" s="47"/>
-      <c r="U16" s="47"/>
-      <c r="V16" s="47"/>
-      <c r="W16" s="47"/>
-      <c r="X16" s="47"/>
-      <c r="Y16" s="47"/>
-      <c r="Z16" s="47"/>
-      <c r="AA16" s="47"/>
-      <c r="AB16" s="47"/>
-      <c r="AC16" s="47"/>
-      <c r="AD16" s="47"/>
-      <c r="AE16" s="47"/>
-      <c r="AF16" s="47"/>
-      <c r="AG16" s="47"/>
-      <c r="AH16" s="47"/>
-      <c r="AI16" s="47"/>
-      <c r="AJ16" s="48"/>
-      <c r="AK16" s="60"/>
-      <c r="AL16" s="61"/>
-      <c r="AM16" s="62"/>
-      <c r="AN16" s="63"/>
-      <c r="AO16" s="63"/>
-      <c r="AP16" s="62"/>
-      <c r="AQ16" s="64"/>
+    <row r="16" spans="1:44" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="42"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="42"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="42"/>
+      <c r="T16" s="42"/>
+      <c r="U16" s="42"/>
+      <c r="V16" s="42"/>
+      <c r="W16" s="42"/>
+      <c r="X16" s="42"/>
+      <c r="Y16" s="42"/>
+      <c r="Z16" s="42"/>
+      <c r="AA16" s="42"/>
+      <c r="AB16" s="42"/>
+      <c r="AC16" s="42"/>
+      <c r="AD16" s="42"/>
+      <c r="AE16" s="42"/>
+      <c r="AF16" s="42"/>
+      <c r="AG16" s="42"/>
+      <c r="AH16" s="42"/>
+      <c r="AI16" s="42"/>
+      <c r="AJ16" s="43"/>
+      <c r="AK16" s="55"/>
+      <c r="AL16" s="56"/>
+      <c r="AM16" s="57"/>
+      <c r="AN16" s="58"/>
+      <c r="AO16" s="58"/>
+      <c r="AP16" s="57"/>
+      <c r="AQ16" s="59"/>
     </row>
-    <row r="17" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="40"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="47"/>
-      <c r="K17" s="47"/>
-      <c r="L17" s="47"/>
-      <c r="M17" s="47"/>
-      <c r="N17" s="47"/>
-      <c r="O17" s="47"/>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="47"/>
-      <c r="R17" s="47"/>
-      <c r="S17" s="47"/>
-      <c r="T17" s="47"/>
-      <c r="U17" s="47"/>
-      <c r="V17" s="47"/>
-      <c r="W17" s="47"/>
-      <c r="X17" s="47"/>
-      <c r="Y17" s="47"/>
-      <c r="Z17" s="47"/>
-      <c r="AA17" s="47"/>
-      <c r="AB17" s="47"/>
-      <c r="AC17" s="47"/>
-      <c r="AD17" s="47"/>
-      <c r="AE17" s="47"/>
-      <c r="AF17" s="47"/>
-      <c r="AG17" s="47"/>
-      <c r="AH17" s="47"/>
-      <c r="AI17" s="47"/>
-      <c r="AJ17" s="48"/>
-      <c r="AK17" s="60"/>
-      <c r="AL17" s="61"/>
-      <c r="AM17" s="62"/>
-      <c r="AN17" s="63"/>
-      <c r="AO17" s="63"/>
-      <c r="AP17" s="62"/>
-      <c r="AQ17" s="64"/>
+    <row r="17" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="35"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="42"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="42"/>
+      <c r="T17" s="42"/>
+      <c r="U17" s="42"/>
+      <c r="V17" s="42"/>
+      <c r="W17" s="42"/>
+      <c r="X17" s="42"/>
+      <c r="Y17" s="42"/>
+      <c r="Z17" s="42"/>
+      <c r="AA17" s="42"/>
+      <c r="AB17" s="42"/>
+      <c r="AC17" s="42"/>
+      <c r="AD17" s="42"/>
+      <c r="AE17" s="42"/>
+      <c r="AF17" s="42"/>
+      <c r="AG17" s="42"/>
+      <c r="AH17" s="42"/>
+      <c r="AI17" s="42"/>
+      <c r="AJ17" s="43"/>
+      <c r="AK17" s="55"/>
+      <c r="AL17" s="56"/>
+      <c r="AM17" s="57"/>
+      <c r="AN17" s="58"/>
+      <c r="AO17" s="58"/>
+      <c r="AP17" s="57"/>
+      <c r="AQ17" s="59"/>
     </row>
-    <row r="18" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="47"/>
-      <c r="M18" s="47"/>
-      <c r="N18" s="47"/>
-      <c r="O18" s="47"/>
-      <c r="P18" s="47"/>
-      <c r="Q18" s="47"/>
-      <c r="R18" s="47"/>
-      <c r="S18" s="47"/>
-      <c r="T18" s="47"/>
-      <c r="U18" s="47"/>
-      <c r="V18" s="47"/>
-      <c r="W18" s="47"/>
-      <c r="X18" s="47"/>
-      <c r="Y18" s="47"/>
-      <c r="Z18" s="47"/>
-      <c r="AA18" s="47"/>
-      <c r="AB18" s="47"/>
-      <c r="AC18" s="47"/>
-      <c r="AD18" s="47"/>
-      <c r="AE18" s="47"/>
-      <c r="AF18" s="47"/>
-      <c r="AG18" s="47"/>
-      <c r="AH18" s="47"/>
-      <c r="AI18" s="47"/>
-      <c r="AJ18" s="48"/>
-      <c r="AK18" s="60"/>
-      <c r="AL18" s="61"/>
-      <c r="AM18" s="62"/>
-      <c r="AN18" s="63"/>
-      <c r="AO18" s="63"/>
-      <c r="AP18" s="62"/>
-      <c r="AQ18" s="64"/>
+    <row r="18" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="35"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="42"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="42"/>
+      <c r="T18" s="42"/>
+      <c r="U18" s="42"/>
+      <c r="V18" s="42"/>
+      <c r="W18" s="42"/>
+      <c r="X18" s="42"/>
+      <c r="Y18" s="42"/>
+      <c r="Z18" s="42"/>
+      <c r="AA18" s="42"/>
+      <c r="AB18" s="42"/>
+      <c r="AC18" s="42"/>
+      <c r="AD18" s="42"/>
+      <c r="AE18" s="42"/>
+      <c r="AF18" s="42"/>
+      <c r="AG18" s="42"/>
+      <c r="AH18" s="42"/>
+      <c r="AI18" s="42"/>
+      <c r="AJ18" s="43"/>
+      <c r="AK18" s="55"/>
+      <c r="AL18" s="56"/>
+      <c r="AM18" s="57"/>
+      <c r="AN18" s="58"/>
+      <c r="AO18" s="58"/>
+      <c r="AP18" s="57"/>
+      <c r="AQ18" s="59"/>
     </row>
-    <row r="19" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
-      <c r="P19" s="47"/>
-      <c r="Q19" s="47"/>
-      <c r="R19" s="47"/>
-      <c r="S19" s="47"/>
-      <c r="T19" s="47"/>
-      <c r="U19" s="47"/>
-      <c r="V19" s="47"/>
-      <c r="W19" s="47"/>
-      <c r="X19" s="47"/>
-      <c r="Y19" s="47"/>
-      <c r="Z19" s="47"/>
-      <c r="AA19" s="47"/>
-      <c r="AB19" s="47"/>
-      <c r="AC19" s="47"/>
-      <c r="AD19" s="47"/>
-      <c r="AE19" s="47"/>
-      <c r="AF19" s="47"/>
-      <c r="AG19" s="47"/>
-      <c r="AH19" s="47"/>
-      <c r="AI19" s="47"/>
-      <c r="AJ19" s="48"/>
-      <c r="AK19" s="60"/>
-      <c r="AL19" s="61"/>
-      <c r="AM19" s="62"/>
-      <c r="AN19" s="63"/>
-      <c r="AO19" s="63"/>
-      <c r="AP19" s="62"/>
-      <c r="AQ19" s="64"/>
+    <row r="19" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="42"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="42"/>
+      <c r="R19" s="42"/>
+      <c r="S19" s="42"/>
+      <c r="T19" s="42"/>
+      <c r="U19" s="42"/>
+      <c r="V19" s="42"/>
+      <c r="W19" s="42"/>
+      <c r="X19" s="42"/>
+      <c r="Y19" s="42"/>
+      <c r="Z19" s="42"/>
+      <c r="AA19" s="42"/>
+      <c r="AB19" s="42"/>
+      <c r="AC19" s="42"/>
+      <c r="AD19" s="42"/>
+      <c r="AE19" s="42"/>
+      <c r="AF19" s="42"/>
+      <c r="AG19" s="42"/>
+      <c r="AH19" s="42"/>
+      <c r="AI19" s="42"/>
+      <c r="AJ19" s="43"/>
+      <c r="AK19" s="55"/>
+      <c r="AL19" s="56"/>
+      <c r="AM19" s="57"/>
+      <c r="AN19" s="58"/>
+      <c r="AO19" s="58"/>
+      <c r="AP19" s="57"/>
+      <c r="AQ19" s="59"/>
     </row>
-    <row r="20" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="47"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="47"/>
-      <c r="R20" s="47"/>
-      <c r="S20" s="47"/>
-      <c r="T20" s="47"/>
-      <c r="U20" s="47"/>
-      <c r="V20" s="47"/>
-      <c r="W20" s="47"/>
-      <c r="X20" s="47"/>
-      <c r="Y20" s="47"/>
-      <c r="Z20" s="47"/>
-      <c r="AA20" s="47"/>
-      <c r="AB20" s="47"/>
-      <c r="AC20" s="47"/>
-      <c r="AD20" s="47"/>
-      <c r="AE20" s="47"/>
-      <c r="AF20" s="47"/>
-      <c r="AG20" s="47"/>
-      <c r="AH20" s="47"/>
-      <c r="AI20" s="47"/>
-      <c r="AJ20" s="48"/>
-      <c r="AK20" s="60"/>
-      <c r="AL20" s="61"/>
-      <c r="AM20" s="62"/>
-      <c r="AN20" s="63"/>
-      <c r="AO20" s="63"/>
-      <c r="AP20" s="62"/>
-      <c r="AQ20" s="64"/>
+    <row r="20" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="35"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="42"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="42"/>
+      <c r="T20" s="42"/>
+      <c r="U20" s="42"/>
+      <c r="V20" s="42"/>
+      <c r="W20" s="42"/>
+      <c r="X20" s="42"/>
+      <c r="Y20" s="42"/>
+      <c r="Z20" s="42"/>
+      <c r="AA20" s="42"/>
+      <c r="AB20" s="42"/>
+      <c r="AC20" s="42"/>
+      <c r="AD20" s="42"/>
+      <c r="AE20" s="42"/>
+      <c r="AF20" s="42"/>
+      <c r="AG20" s="42"/>
+      <c r="AH20" s="42"/>
+      <c r="AI20" s="42"/>
+      <c r="AJ20" s="43"/>
+      <c r="AK20" s="55"/>
+      <c r="AL20" s="56"/>
+      <c r="AM20" s="57"/>
+      <c r="AN20" s="58"/>
+      <c r="AO20" s="58"/>
+      <c r="AP20" s="57"/>
+      <c r="AQ20" s="59"/>
     </row>
-    <row r="21" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="47"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="47"/>
-      <c r="Q21" s="47"/>
-      <c r="R21" s="47"/>
-      <c r="S21" s="47"/>
-      <c r="T21" s="47"/>
-      <c r="U21" s="47"/>
-      <c r="V21" s="47"/>
-      <c r="W21" s="47"/>
-      <c r="X21" s="47"/>
-      <c r="Y21" s="47"/>
-      <c r="Z21" s="47"/>
-      <c r="AA21" s="47"/>
-      <c r="AB21" s="47"/>
-      <c r="AC21" s="47"/>
-      <c r="AD21" s="47"/>
-      <c r="AE21" s="47"/>
-      <c r="AF21" s="47"/>
-      <c r="AG21" s="47"/>
-      <c r="AH21" s="47"/>
-      <c r="AI21" s="47"/>
-      <c r="AJ21" s="48"/>
-      <c r="AK21" s="60"/>
-      <c r="AL21" s="61"/>
-      <c r="AM21" s="62"/>
-      <c r="AN21" s="63"/>
-      <c r="AO21" s="63"/>
-      <c r="AP21" s="62"/>
-      <c r="AQ21" s="64"/>
+    <row r="21" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="35"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="42"/>
+      <c r="R21" s="42"/>
+      <c r="S21" s="42"/>
+      <c r="T21" s="42"/>
+      <c r="U21" s="42"/>
+      <c r="V21" s="42"/>
+      <c r="W21" s="42"/>
+      <c r="X21" s="42"/>
+      <c r="Y21" s="42"/>
+      <c r="Z21" s="42"/>
+      <c r="AA21" s="42"/>
+      <c r="AB21" s="42"/>
+      <c r="AC21" s="42"/>
+      <c r="AD21" s="42"/>
+      <c r="AE21" s="42"/>
+      <c r="AF21" s="42"/>
+      <c r="AG21" s="42"/>
+      <c r="AH21" s="42"/>
+      <c r="AI21" s="42"/>
+      <c r="AJ21" s="43"/>
+      <c r="AK21" s="55"/>
+      <c r="AL21" s="56"/>
+      <c r="AM21" s="57"/>
+      <c r="AN21" s="58"/>
+      <c r="AO21" s="58"/>
+      <c r="AP21" s="57"/>
+      <c r="AQ21" s="59"/>
     </row>
-    <row r="22" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="47"/>
-      <c r="M22" s="47"/>
-      <c r="N22" s="47"/>
-      <c r="O22" s="47"/>
-      <c r="P22" s="47"/>
-      <c r="Q22" s="47"/>
-      <c r="R22" s="47"/>
-      <c r="S22" s="47"/>
-      <c r="T22" s="47"/>
-      <c r="U22" s="47"/>
-      <c r="V22" s="47"/>
-      <c r="W22" s="47"/>
-      <c r="X22" s="47"/>
-      <c r="Y22" s="47"/>
-      <c r="Z22" s="47"/>
-      <c r="AA22" s="47"/>
-      <c r="AB22" s="47"/>
-      <c r="AC22" s="47"/>
-      <c r="AD22" s="47"/>
-      <c r="AE22" s="47"/>
-      <c r="AF22" s="47"/>
-      <c r="AG22" s="47"/>
-      <c r="AH22" s="47"/>
-      <c r="AI22" s="47"/>
-      <c r="AJ22" s="48"/>
-      <c r="AK22" s="60"/>
-      <c r="AL22" s="61"/>
-      <c r="AM22" s="62"/>
-      <c r="AN22" s="63"/>
-      <c r="AO22" s="63"/>
-      <c r="AP22" s="62"/>
-      <c r="AQ22" s="64"/>
+    <row r="22" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="35"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="42"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="42"/>
+      <c r="R22" s="42"/>
+      <c r="S22" s="42"/>
+      <c r="T22" s="42"/>
+      <c r="U22" s="42"/>
+      <c r="V22" s="42"/>
+      <c r="W22" s="42"/>
+      <c r="X22" s="42"/>
+      <c r="Y22" s="42"/>
+      <c r="Z22" s="42"/>
+      <c r="AA22" s="42"/>
+      <c r="AB22" s="42"/>
+      <c r="AC22" s="42"/>
+      <c r="AD22" s="42"/>
+      <c r="AE22" s="42"/>
+      <c r="AF22" s="42"/>
+      <c r="AG22" s="42"/>
+      <c r="AH22" s="42"/>
+      <c r="AI22" s="42"/>
+      <c r="AJ22" s="43"/>
+      <c r="AK22" s="55"/>
+      <c r="AL22" s="56"/>
+      <c r="AM22" s="57"/>
+      <c r="AN22" s="58"/>
+      <c r="AO22" s="58"/>
+      <c r="AP22" s="57"/>
+      <c r="AQ22" s="59"/>
     </row>
-    <row r="23" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47"/>
-      <c r="O23" s="47"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47"/>
-      <c r="S23" s="47"/>
-      <c r="T23" s="47"/>
-      <c r="U23" s="47"/>
-      <c r="V23" s="47"/>
-      <c r="W23" s="47"/>
-      <c r="X23" s="47"/>
-      <c r="Y23" s="47"/>
-      <c r="Z23" s="47"/>
-      <c r="AA23" s="47"/>
-      <c r="AB23" s="47"/>
-      <c r="AC23" s="47"/>
-      <c r="AD23" s="47"/>
-      <c r="AE23" s="47"/>
-      <c r="AF23" s="47"/>
-      <c r="AG23" s="47"/>
-      <c r="AH23" s="47"/>
-      <c r="AI23" s="47"/>
-      <c r="AJ23" s="48"/>
-      <c r="AK23" s="60"/>
-      <c r="AL23" s="61"/>
-      <c r="AM23" s="62"/>
-      <c r="AN23" s="63"/>
-      <c r="AO23" s="63"/>
-      <c r="AP23" s="62"/>
-      <c r="AQ23" s="64"/>
+    <row r="23" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="42"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="42"/>
+      <c r="R23" s="42"/>
+      <c r="S23" s="42"/>
+      <c r="T23" s="42"/>
+      <c r="U23" s="42"/>
+      <c r="V23" s="42"/>
+      <c r="W23" s="42"/>
+      <c r="X23" s="42"/>
+      <c r="Y23" s="42"/>
+      <c r="Z23" s="42"/>
+      <c r="AA23" s="42"/>
+      <c r="AB23" s="42"/>
+      <c r="AC23" s="42"/>
+      <c r="AD23" s="42"/>
+      <c r="AE23" s="42"/>
+      <c r="AF23" s="42"/>
+      <c r="AG23" s="42"/>
+      <c r="AH23" s="42"/>
+      <c r="AI23" s="42"/>
+      <c r="AJ23" s="43"/>
+      <c r="AK23" s="55"/>
+      <c r="AL23" s="56"/>
+      <c r="AM23" s="57"/>
+      <c r="AN23" s="58"/>
+      <c r="AO23" s="58"/>
+      <c r="AP23" s="57"/>
+      <c r="AQ23" s="59"/>
     </row>
-    <row r="24" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="40"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
-      <c r="O24" s="47"/>
-      <c r="P24" s="47"/>
-      <c r="Q24" s="47"/>
-      <c r="R24" s="47"/>
-      <c r="S24" s="47"/>
-      <c r="T24" s="47"/>
-      <c r="U24" s="47"/>
-      <c r="V24" s="47"/>
-      <c r="W24" s="47"/>
-      <c r="X24" s="47"/>
-      <c r="Y24" s="47"/>
-      <c r="Z24" s="47"/>
-      <c r="AA24" s="47"/>
-      <c r="AB24" s="47"/>
-      <c r="AC24" s="47"/>
-      <c r="AD24" s="47"/>
-      <c r="AE24" s="47"/>
-      <c r="AF24" s="47"/>
-      <c r="AG24" s="47"/>
-      <c r="AH24" s="47"/>
-      <c r="AI24" s="47"/>
-      <c r="AJ24" s="48"/>
-      <c r="AK24" s="60"/>
-      <c r="AL24" s="61"/>
-      <c r="AM24" s="62"/>
-      <c r="AN24" s="63"/>
-      <c r="AO24" s="63"/>
-      <c r="AP24" s="62"/>
-      <c r="AQ24" s="64"/>
+    <row r="24" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="35"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
+      <c r="S24" s="42"/>
+      <c r="T24" s="42"/>
+      <c r="U24" s="42"/>
+      <c r="V24" s="42"/>
+      <c r="W24" s="42"/>
+      <c r="X24" s="42"/>
+      <c r="Y24" s="42"/>
+      <c r="Z24" s="42"/>
+      <c r="AA24" s="42"/>
+      <c r="AB24" s="42"/>
+      <c r="AC24" s="42"/>
+      <c r="AD24" s="42"/>
+      <c r="AE24" s="42"/>
+      <c r="AF24" s="42"/>
+      <c r="AG24" s="42"/>
+      <c r="AH24" s="42"/>
+      <c r="AI24" s="42"/>
+      <c r="AJ24" s="43"/>
+      <c r="AK24" s="55"/>
+      <c r="AL24" s="56"/>
+      <c r="AM24" s="57"/>
+      <c r="AN24" s="58"/>
+      <c r="AO24" s="58"/>
+      <c r="AP24" s="57"/>
+      <c r="AQ24" s="59"/>
     </row>
-    <row r="25" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="40"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="47"/>
-      <c r="O25" s="47"/>
-      <c r="P25" s="47"/>
-      <c r="Q25" s="47"/>
-      <c r="R25" s="47"/>
-      <c r="S25" s="47"/>
-      <c r="T25" s="47"/>
-      <c r="U25" s="47"/>
-      <c r="V25" s="47"/>
-      <c r="W25" s="47"/>
-      <c r="X25" s="47"/>
-      <c r="Y25" s="47"/>
-      <c r="Z25" s="47"/>
-      <c r="AA25" s="47"/>
-      <c r="AB25" s="47"/>
-      <c r="AC25" s="47"/>
-      <c r="AD25" s="47"/>
-      <c r="AE25" s="47"/>
-      <c r="AF25" s="47"/>
-      <c r="AG25" s="47"/>
-      <c r="AH25" s="47"/>
-      <c r="AI25" s="47"/>
-      <c r="AJ25" s="48"/>
-      <c r="AK25" s="60"/>
-      <c r="AL25" s="61"/>
-      <c r="AM25" s="62"/>
-      <c r="AN25" s="63"/>
-      <c r="AO25" s="63"/>
-      <c r="AP25" s="62"/>
-      <c r="AQ25" s="64"/>
+    <row r="25" spans="1:43" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="35"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="42"/>
+      <c r="O25" s="42"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="42"/>
+      <c r="R25" s="42"/>
+      <c r="S25" s="42"/>
+      <c r="T25" s="42"/>
+      <c r="U25" s="42"/>
+      <c r="V25" s="42"/>
+      <c r="W25" s="42"/>
+      <c r="X25" s="42"/>
+      <c r="Y25" s="42"/>
+      <c r="Z25" s="42"/>
+      <c r="AA25" s="42"/>
+      <c r="AB25" s="42"/>
+      <c r="AC25" s="42"/>
+      <c r="AD25" s="42"/>
+      <c r="AE25" s="42"/>
+      <c r="AF25" s="42"/>
+      <c r="AG25" s="42"/>
+      <c r="AH25" s="42"/>
+      <c r="AI25" s="42"/>
+      <c r="AJ25" s="43"/>
+      <c r="AK25" s="55"/>
+      <c r="AL25" s="56"/>
+      <c r="AM25" s="57"/>
+      <c r="AN25" s="58"/>
+      <c r="AO25" s="58"/>
+      <c r="AP25" s="57"/>
+      <c r="AQ25" s="59"/>
     </row>
-    <row r="26" spans="1:43" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="41"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="50"/>
-      <c r="M26" s="50"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="50"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="X26" s="50"/>
-      <c r="Y26" s="50"/>
-      <c r="Z26" s="50"/>
-      <c r="AA26" s="50"/>
-      <c r="AB26" s="50"/>
-      <c r="AC26" s="50"/>
-      <c r="AD26" s="50"/>
-      <c r="AE26" s="50"/>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="51"/>
-      <c r="AK26" s="65"/>
-      <c r="AL26" s="66"/>
-      <c r="AM26" s="67"/>
-      <c r="AN26" s="68"/>
-      <c r="AO26" s="68"/>
-      <c r="AP26" s="67"/>
-      <c r="AQ26" s="69"/>
+    <row r="26" spans="1:43" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="36"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="45"/>
+      <c r="R26" s="45"/>
+      <c r="S26" s="45"/>
+      <c r="T26" s="45"/>
+      <c r="U26" s="45"/>
+      <c r="V26" s="45"/>
+      <c r="W26" s="45"/>
+      <c r="X26" s="45"/>
+      <c r="Y26" s="45"/>
+      <c r="Z26" s="45"/>
+      <c r="AA26" s="45"/>
+      <c r="AB26" s="45"/>
+      <c r="AC26" s="45"/>
+      <c r="AD26" s="45"/>
+      <c r="AE26" s="45"/>
+      <c r="AF26" s="45"/>
+      <c r="AG26" s="45"/>
+      <c r="AH26" s="45"/>
+      <c r="AI26" s="45"/>
+      <c r="AJ26" s="46"/>
+      <c r="AK26" s="60"/>
+      <c r="AL26" s="61"/>
+      <c r="AM26" s="62"/>
+      <c r="AN26" s="63"/>
+      <c r="AO26" s="63"/>
+      <c r="AP26" s="62"/>
+      <c r="AQ26" s="64"/>
     </row>
-    <row r="27" spans="1:43" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="70" t="s">
+    <row r="27" spans="1:43" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="71"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="71"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="71"/>
-      <c r="O27" s="71"/>
-      <c r="P27" s="71"/>
-      <c r="Q27" s="71"/>
-      <c r="R27" s="71"/>
-      <c r="S27" s="71"/>
-      <c r="T27" s="71"/>
-      <c r="U27" s="71"/>
-      <c r="V27" s="71"/>
-      <c r="W27" s="71"/>
-      <c r="X27" s="71"/>
-      <c r="Y27" s="71"/>
-      <c r="Z27" s="71"/>
-      <c r="AA27" s="71"/>
-      <c r="AB27" s="71"/>
-      <c r="AC27" s="71"/>
-      <c r="AD27" s="71"/>
-      <c r="AE27" s="71"/>
-      <c r="AF27" s="71"/>
-      <c r="AG27" s="71"/>
-      <c r="AH27" s="71"/>
-      <c r="AI27" s="71"/>
-      <c r="AJ27" s="75"/>
-      <c r="AK27" s="152" t="s">
+      <c r="B27" s="66"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="66"/>
+      <c r="J27" s="66"/>
+      <c r="K27" s="66"/>
+      <c r="L27" s="66"/>
+      <c r="M27" s="66"/>
+      <c r="N27" s="66"/>
+      <c r="O27" s="66"/>
+      <c r="P27" s="66"/>
+      <c r="Q27" s="66"/>
+      <c r="R27" s="66"/>
+      <c r="S27" s="66"/>
+      <c r="T27" s="66"/>
+      <c r="U27" s="66"/>
+      <c r="V27" s="66"/>
+      <c r="W27" s="66"/>
+      <c r="X27" s="66"/>
+      <c r="Y27" s="66"/>
+      <c r="Z27" s="66"/>
+      <c r="AA27" s="66"/>
+      <c r="AB27" s="66"/>
+      <c r="AC27" s="66"/>
+      <c r="AD27" s="66"/>
+      <c r="AE27" s="66"/>
+      <c r="AF27" s="66"/>
+      <c r="AG27" s="66"/>
+      <c r="AH27" s="66"/>
+      <c r="AI27" s="66"/>
+      <c r="AJ27" s="70"/>
+      <c r="AK27" s="127" t="s">
         <v>10</v>
       </c>
-      <c r="AL27" s="153"/>
-      <c r="AM27" s="153"/>
-      <c r="AN27" s="153"/>
-      <c r="AO27" s="153"/>
-      <c r="AP27" s="153"/>
-      <c r="AQ27" s="154"/>
+      <c r="AL27" s="128"/>
+      <c r="AM27" s="128"/>
+      <c r="AN27" s="128"/>
+      <c r="AO27" s="128"/>
+      <c r="AP27" s="128"/>
+      <c r="AQ27" s="129"/>
     </row>
-    <row r="28" spans="1:43" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="72"/>
-      <c r="B28" s="73"/>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="74" t="s">
+    <row r="28" spans="1:43" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="67"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="73"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="73"/>
-      <c r="J28" s="73"/>
-      <c r="K28" s="73"/>
-      <c r="L28" s="73"/>
-      <c r="M28" s="73"/>
-      <c r="N28" s="73"/>
-      <c r="O28" s="73"/>
-      <c r="P28" s="73"/>
-      <c r="Q28" s="73"/>
-      <c r="R28" s="73"/>
-      <c r="S28" s="73"/>
-      <c r="T28" s="73"/>
-      <c r="U28" s="74" t="s">
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="68"/>
+      <c r="N28" s="68"/>
+      <c r="O28" s="68"/>
+      <c r="P28" s="68"/>
+      <c r="Q28" s="68"/>
+      <c r="R28" s="68"/>
+      <c r="S28" s="68"/>
+      <c r="T28" s="68"/>
+      <c r="U28" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="V28" s="73"/>
-      <c r="W28" s="73"/>
-      <c r="X28" s="73"/>
-      <c r="Y28" s="73"/>
-      <c r="Z28" s="73"/>
-      <c r="AA28" s="73"/>
-      <c r="AB28" s="73"/>
-      <c r="AC28" s="73"/>
-      <c r="AD28" s="73"/>
-      <c r="AE28" s="73"/>
-      <c r="AF28" s="73"/>
-      <c r="AG28" s="73"/>
-      <c r="AH28" s="73"/>
-      <c r="AI28" s="73"/>
-      <c r="AJ28" s="76"/>
-      <c r="AK28" s="136" t="s">
+      <c r="V28" s="68"/>
+      <c r="W28" s="68"/>
+      <c r="X28" s="68"/>
+      <c r="Y28" s="68"/>
+      <c r="Z28" s="68"/>
+      <c r="AA28" s="68"/>
+      <c r="AB28" s="68"/>
+      <c r="AC28" s="68"/>
+      <c r="AD28" s="68"/>
+      <c r="AE28" s="68"/>
+      <c r="AF28" s="68"/>
+      <c r="AG28" s="68"/>
+      <c r="AH28" s="68"/>
+      <c r="AI28" s="68"/>
+      <c r="AJ28" s="71"/>
+      <c r="AK28" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="AL28" s="137"/>
-      <c r="AM28" s="137"/>
-      <c r="AN28" s="137"/>
-      <c r="AO28" s="137"/>
-      <c r="AP28" s="137"/>
-      <c r="AQ28" s="138"/>
+      <c r="AL28" s="112"/>
+      <c r="AM28" s="112"/>
+      <c r="AN28" s="112"/>
+      <c r="AO28" s="112"/>
+      <c r="AP28" s="112"/>
+      <c r="AQ28" s="113"/>
     </row>
-    <row r="29" spans="1:43" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="X29" s="31"/>
+    <row r="29" spans="1:43" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="X29" s="15"/>
       <c r="AC29" s="3"/>
       <c r="AP29" s="2"/>
     </row>
-    <row r="30" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="31"/>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="31"/>
+    <row r="30" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15"/>
     </row>
-    <row r="40" spans="2:17" ht="21.75" x14ac:dyDescent="0.2">
-      <c r="B40" s="31" t="s">
+    <row r="40" spans="2:17" ht="21.6" x14ac:dyDescent="0.25">
+      <c r="B40" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="31"/>
-      <c r="M40" s="31"/>
-      <c r="N40" s="31"/>
-      <c r="O40" s="31"/>
-      <c r="P40" s="31"/>
-      <c r="Q40" s="31"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="15"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
     </row>
-    <row r="41" spans="2:17" ht="21.75" x14ac:dyDescent="0.2">
-      <c r="B41" s="31" t="s">
+    <row r="41" spans="2:17" ht="21.6" x14ac:dyDescent="0.25">
+      <c r="B41" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="31"/>
-      <c r="L41" s="31"/>
-      <c r="M41" s="31"/>
-      <c r="N41" s="31"/>
-      <c r="O41" s="31"/>
-      <c r="P41" s="31"/>
-      <c r="Q41" s="31"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="15"/>
+      <c r="P41" s="15"/>
+      <c r="Q41" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="46">

--- a/assets/frm-eib04-template.xlsx
+++ b/assets/frm-eib04-template.xlsx
@@ -1570,6 +1570,214 @@
         </a:extLst>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>130171</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>28576</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>148163</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>314326</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3001" name="ValueBox Month"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>{{MONTH}}</a:t>
+          </a:r>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>17992</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>303742</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3002" name="ValueBox Year"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>{{YEAR}}</a:t>
+          </a:r>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3003" name="ValueBox Group"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>{{GROUP}}</a:t>
+          </a:r>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>68787</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>150000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>361951</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3004" name="ValueBox Unit"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>{{UNIT}}</a:t>
+          </a:r>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>402167</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>254002</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>582083</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>380999</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3005" name="ValueBox Section"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="b"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>{{SECTION}}</a:t>
+          </a:r>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -7013,27 +7221,19 @@
       <c r="AQ3" s="102"/>
     </row>
     <row r="4" spans="1:44" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                                   Month  {{MONTH}} Year {{YEAR}}</t>
-        </is>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:44" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">กลุ่มเครื่องตรวจ เครื่องวัดและเครื่องทดสอบ (Inspection, measuring and testing instruments group) {{GROUP}}</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">หน่วยงาน (Unit) {{UNIT}}</t>
-        </is>
-      </c>
-      <c r="AN5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">แผนก (Section) {{SECTION}}</t>
-        </is>
+      <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:44" s="3" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/assets/frm-eib04-template.xlsx
+++ b/assets/frm-eib04-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\8014\Desktop\calibration-system-main\ตัวอย่าง\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F33F982-8F4E-4DF8-9DF4-EB1AEC33A7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12E9A9A-2F12-4D85-8CF5-4D7E578948C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1048,6 +1048,174 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1058,15 +1226,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1093,77 +1252,68 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1174,12 +1324,6 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1221,150 +1365,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -1500,16 +1500,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>24764</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>247650</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>114299</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1539,8 +1539,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3514725" y="85725"/>
-          <a:ext cx="428625" cy="457200"/>
+          <a:off x="4010024" y="15240"/>
+          <a:ext cx="523875" cy="544830"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7155,15 +7155,15 @@
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="19.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13" style="1" customWidth="1"/>
     <col min="4" max="4" width="6.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.33203125" style="1" customWidth="1"/>
     <col min="6" max="14" width="2.109375" style="1" customWidth="1"/>
     <col min="15" max="17" width="2.5546875" style="1" customWidth="1"/>
     <col min="18" max="18" width="2.44140625" style="1" customWidth="1"/>
     <col min="19" max="36" width="2.5546875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="9" style="1" customWidth="1"/>
+    <col min="37" max="37" width="8.109375" style="1" customWidth="1"/>
     <col min="38" max="38" width="7.44140625" style="1" customWidth="1"/>
     <col min="39" max="39" width="8.44140625" style="1" customWidth="1"/>
     <col min="40" max="43" width="9.44140625" style="1" customWidth="1"/>
@@ -7174,51 +7174,51 @@
       <c r="AO1" s="2"/>
     </row>
     <row r="3" spans="1:44" ht="29.25" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A3" s="102" t="s">
+      <c r="A3" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="102"/>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="102"/>
-      <c r="S3" s="102"/>
-      <c r="T3" s="102"/>
-      <c r="U3" s="102"/>
-      <c r="V3" s="102"/>
-      <c r="W3" s="102"/>
-      <c r="X3" s="102"/>
-      <c r="Y3" s="102"/>
-      <c r="Z3" s="102"/>
-      <c r="AA3" s="102"/>
-      <c r="AB3" s="102"/>
-      <c r="AC3" s="102"/>
-      <c r="AD3" s="102"/>
-      <c r="AE3" s="102"/>
-      <c r="AF3" s="102"/>
-      <c r="AG3" s="102"/>
-      <c r="AH3" s="102"/>
-      <c r="AI3" s="102"/>
-      <c r="AJ3" s="102"/>
-      <c r="AK3" s="102"/>
-      <c r="AL3" s="102"/>
-      <c r="AM3" s="102"/>
-      <c r="AN3" s="102"/>
-      <c r="AO3" s="102"/>
-      <c r="AP3" s="102"/>
-      <c r="AQ3" s="102"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="103"/>
+      <c r="O3" s="103"/>
+      <c r="P3" s="103"/>
+      <c r="Q3" s="103"/>
+      <c r="R3" s="103"/>
+      <c r="S3" s="103"/>
+      <c r="T3" s="103"/>
+      <c r="U3" s="103"/>
+      <c r="V3" s="103"/>
+      <c r="W3" s="103"/>
+      <c r="X3" s="103"/>
+      <c r="Y3" s="103"/>
+      <c r="Z3" s="103"/>
+      <c r="AA3" s="103"/>
+      <c r="AB3" s="103"/>
+      <c r="AC3" s="103"/>
+      <c r="AD3" s="103"/>
+      <c r="AE3" s="103"/>
+      <c r="AF3" s="103"/>
+      <c r="AG3" s="103"/>
+      <c r="AH3" s="103"/>
+      <c r="AI3" s="103"/>
+      <c r="AJ3" s="103"/>
+      <c r="AK3" s="103"/>
+      <c r="AL3" s="103"/>
+      <c r="AM3" s="103"/>
+      <c r="AN3" s="103"/>
+      <c r="AO3" s="103"/>
+      <c r="AP3" s="103"/>
+      <c r="AQ3" s="103"/>
     </row>
     <row r="4" spans="1:44" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F4" s="2" t="s">
@@ -7265,221 +7265,221 @@
       </c>
     </row>
     <row r="7" spans="1:44" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="75" t="s">
+      <c r="C7" s="114" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="78" t="s">
+      <c r="D7" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="81" t="s">
+      <c r="E7" s="134" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="84" t="s">
+      <c r="F7" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="85"/>
-      <c r="K7" s="85"/>
-      <c r="L7" s="85"/>
-      <c r="M7" s="85"/>
-      <c r="N7" s="85"/>
-      <c r="O7" s="85"/>
-      <c r="P7" s="85"/>
-      <c r="Q7" s="85"/>
-      <c r="R7" s="85"/>
-      <c r="S7" s="85"/>
-      <c r="T7" s="85"/>
-      <c r="U7" s="85"/>
-      <c r="V7" s="85"/>
-      <c r="W7" s="85"/>
-      <c r="X7" s="85"/>
-      <c r="Y7" s="85"/>
-      <c r="Z7" s="85"/>
-      <c r="AA7" s="85"/>
-      <c r="AB7" s="85"/>
-      <c r="AC7" s="85"/>
-      <c r="AD7" s="85"/>
-      <c r="AE7" s="85"/>
-      <c r="AF7" s="85"/>
-      <c r="AG7" s="85"/>
-      <c r="AH7" s="85"/>
-      <c r="AI7" s="85"/>
-      <c r="AJ7" s="86"/>
-      <c r="AK7" s="109" t="s">
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="138"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="138"/>
+      <c r="M7" s="138"/>
+      <c r="N7" s="138"/>
+      <c r="O7" s="138"/>
+      <c r="P7" s="138"/>
+      <c r="Q7" s="138"/>
+      <c r="R7" s="138"/>
+      <c r="S7" s="138"/>
+      <c r="T7" s="138"/>
+      <c r="U7" s="138"/>
+      <c r="V7" s="138"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="138"/>
+      <c r="Y7" s="138"/>
+      <c r="Z7" s="138"/>
+      <c r="AA7" s="138"/>
+      <c r="AB7" s="138"/>
+      <c r="AC7" s="138"/>
+      <c r="AD7" s="138"/>
+      <c r="AE7" s="138"/>
+      <c r="AF7" s="138"/>
+      <c r="AG7" s="138"/>
+      <c r="AH7" s="138"/>
+      <c r="AI7" s="138"/>
+      <c r="AJ7" s="139"/>
+      <c r="AK7" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="AL7" s="109"/>
-      <c r="AM7" s="109"/>
-      <c r="AN7" s="109"/>
-      <c r="AO7" s="109"/>
-      <c r="AP7" s="109"/>
-      <c r="AQ7" s="110"/>
+      <c r="AL7" s="112"/>
+      <c r="AM7" s="112"/>
+      <c r="AN7" s="112"/>
+      <c r="AO7" s="112"/>
+      <c r="AP7" s="112"/>
+      <c r="AQ7" s="113"/>
     </row>
     <row r="8" spans="1:44" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="76"/>
-      <c r="B8" s="73"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="98">
+      <c r="A8" s="115"/>
+      <c r="B8" s="129"/>
+      <c r="C8" s="115"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="126">
         <v>1</v>
       </c>
-      <c r="G8" s="87">
+      <c r="G8" s="104">
         <v>2</v>
       </c>
-      <c r="H8" s="87">
+      <c r="H8" s="104">
         <v>3</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="104">
         <v>4</v>
       </c>
-      <c r="J8" s="87">
+      <c r="J8" s="104">
         <v>5</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="104">
         <v>6</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="104">
         <v>7</v>
       </c>
-      <c r="M8" s="87">
+      <c r="M8" s="104">
         <v>8</v>
       </c>
-      <c r="N8" s="87">
+      <c r="N8" s="104">
         <v>9</v>
       </c>
-      <c r="O8" s="87">
+      <c r="O8" s="104">
         <v>10</v>
       </c>
-      <c r="P8" s="87">
+      <c r="P8" s="104">
         <v>11</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="104">
         <v>12</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="104">
         <v>13</v>
       </c>
-      <c r="S8" s="87">
+      <c r="S8" s="104">
         <v>14</v>
       </c>
-      <c r="T8" s="87">
+      <c r="T8" s="104">
         <v>15</v>
       </c>
-      <c r="U8" s="87">
+      <c r="U8" s="104">
         <v>16</v>
       </c>
-      <c r="V8" s="87">
+      <c r="V8" s="104">
         <v>17</v>
       </c>
-      <c r="W8" s="87">
+      <c r="W8" s="104">
         <v>18</v>
       </c>
-      <c r="X8" s="87">
+      <c r="X8" s="104">
         <v>19</v>
       </c>
-      <c r="Y8" s="87">
+      <c r="Y8" s="104">
         <v>20</v>
       </c>
-      <c r="Z8" s="87">
+      <c r="Z8" s="104">
         <v>21</v>
       </c>
-      <c r="AA8" s="87">
+      <c r="AA8" s="104">
         <v>22</v>
       </c>
-      <c r="AB8" s="87">
+      <c r="AB8" s="104">
         <v>23</v>
       </c>
-      <c r="AC8" s="87">
+      <c r="AC8" s="104">
         <v>24</v>
       </c>
-      <c r="AD8" s="87">
+      <c r="AD8" s="104">
         <v>25</v>
       </c>
-      <c r="AE8" s="87">
+      <c r="AE8" s="104">
         <v>26</v>
       </c>
-      <c r="AF8" s="87">
+      <c r="AF8" s="104">
         <v>27</v>
       </c>
-      <c r="AG8" s="87">
+      <c r="AG8" s="104">
         <v>28</v>
       </c>
-      <c r="AH8" s="87">
+      <c r="AH8" s="104">
         <v>29</v>
       </c>
-      <c r="AI8" s="87">
+      <c r="AI8" s="104">
         <v>30</v>
       </c>
-      <c r="AJ8" s="103">
+      <c r="AJ8" s="106">
         <v>31</v>
       </c>
-      <c r="AK8" s="105" t="s">
+      <c r="AK8" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="AL8" s="107" t="s">
+      <c r="AL8" s="110" t="s">
         <v>13</v>
       </c>
-      <c r="AM8" s="100" t="s">
+      <c r="AM8" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="AN8" s="95" t="s">
+      <c r="AN8" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="AO8" s="96"/>
-      <c r="AP8" s="95" t="s">
+      <c r="AO8" s="124"/>
+      <c r="AP8" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="97"/>
+      <c r="AQ8" s="125"/>
     </row>
     <row r="9" spans="1:44" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="77"/>
-      <c r="B9" s="74"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="88"/>
-      <c r="H9" s="88"/>
-      <c r="I9" s="88"/>
-      <c r="J9" s="88"/>
-      <c r="K9" s="88"/>
-      <c r="L9" s="88"/>
-      <c r="M9" s="88"/>
-      <c r="N9" s="88"/>
-      <c r="O9" s="88"/>
-      <c r="P9" s="88"/>
-      <c r="Q9" s="88"/>
-      <c r="R9" s="88"/>
-      <c r="S9" s="88"/>
-      <c r="T9" s="88"/>
-      <c r="U9" s="88"/>
-      <c r="V9" s="88"/>
-      <c r="W9" s="88"/>
-      <c r="X9" s="88"/>
-      <c r="Y9" s="88"/>
-      <c r="Z9" s="88"/>
-      <c r="AA9" s="88"/>
-      <c r="AB9" s="88"/>
-      <c r="AC9" s="88"/>
-      <c r="AD9" s="88"/>
-      <c r="AE9" s="88"/>
-      <c r="AF9" s="88"/>
-      <c r="AG9" s="88"/>
-      <c r="AH9" s="88"/>
-      <c r="AI9" s="88"/>
-      <c r="AJ9" s="104"/>
-      <c r="AK9" s="106"/>
-      <c r="AL9" s="108"/>
-      <c r="AM9" s="101"/>
+      <c r="A9" s="116"/>
+      <c r="B9" s="130"/>
+      <c r="C9" s="116"/>
+      <c r="D9" s="133"/>
+      <c r="E9" s="136"/>
+      <c r="F9" s="127"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="105"/>
+      <c r="N9" s="105"/>
+      <c r="O9" s="105"/>
+      <c r="P9" s="105"/>
+      <c r="Q9" s="105"/>
+      <c r="R9" s="105"/>
+      <c r="S9" s="105"/>
+      <c r="T9" s="105"/>
+      <c r="U9" s="105"/>
+      <c r="V9" s="105"/>
+      <c r="W9" s="105"/>
+      <c r="X9" s="105"/>
+      <c r="Y9" s="105"/>
+      <c r="Z9" s="105"/>
+      <c r="AA9" s="105"/>
+      <c r="AB9" s="105"/>
+      <c r="AC9" s="105"/>
+      <c r="AD9" s="105"/>
+      <c r="AE9" s="105"/>
+      <c r="AF9" s="105"/>
+      <c r="AG9" s="105"/>
+      <c r="AH9" s="105"/>
+      <c r="AI9" s="105"/>
+      <c r="AJ9" s="107"/>
+      <c r="AK9" s="109"/>
+      <c r="AL9" s="111"/>
+      <c r="AM9" s="102"/>
       <c r="AN9" s="4" t="s">
         <v>12</v>
       </c>
@@ -7496,6 +7496,34 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:AJ7"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="AN8:AO8"/>
+    <mergeCell ref="AP8:AQ8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
     <mergeCell ref="AM8:AM9"/>
     <mergeCell ref="A3:AQ3"/>
     <mergeCell ref="AF8:AF9"/>
@@ -7512,34 +7540,6 @@
     <mergeCell ref="AL8:AL9"/>
     <mergeCell ref="AK7:AQ7"/>
     <mergeCell ref="A7:A9"/>
-    <mergeCell ref="AN8:AO8"/>
-    <mergeCell ref="AP8:AQ8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:AJ7"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="T8:T9"/>
   </mergeCells>
   <pageMargins left="0.27559055118110237" right="0.23622047244094491" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="77" orientation="landscape" r:id="rId1"/>
@@ -7576,51 +7576,51 @@
       <c r="AO1" s="2"/>
     </row>
     <row r="3" spans="1:44" ht="29.25" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A3" s="102" t="s">
+      <c r="A3" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="102"/>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="102"/>
-      <c r="S3" s="102"/>
-      <c r="T3" s="102"/>
-      <c r="U3" s="102"/>
-      <c r="V3" s="102"/>
-      <c r="W3" s="102"/>
-      <c r="X3" s="102"/>
-      <c r="Y3" s="102"/>
-      <c r="Z3" s="102"/>
-      <c r="AA3" s="102"/>
-      <c r="AB3" s="102"/>
-      <c r="AC3" s="102"/>
-      <c r="AD3" s="102"/>
-      <c r="AE3" s="102"/>
-      <c r="AF3" s="102"/>
-      <c r="AG3" s="102"/>
-      <c r="AH3" s="102"/>
-      <c r="AI3" s="102"/>
-      <c r="AJ3" s="102"/>
-      <c r="AK3" s="102"/>
-      <c r="AL3" s="102"/>
-      <c r="AM3" s="102"/>
-      <c r="AN3" s="102"/>
-      <c r="AO3" s="102"/>
-      <c r="AP3" s="102"/>
-      <c r="AQ3" s="102"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="103"/>
+      <c r="O3" s="103"/>
+      <c r="P3" s="103"/>
+      <c r="Q3" s="103"/>
+      <c r="R3" s="103"/>
+      <c r="S3" s="103"/>
+      <c r="T3" s="103"/>
+      <c r="U3" s="103"/>
+      <c r="V3" s="103"/>
+      <c r="W3" s="103"/>
+      <c r="X3" s="103"/>
+      <c r="Y3" s="103"/>
+      <c r="Z3" s="103"/>
+      <c r="AA3" s="103"/>
+      <c r="AB3" s="103"/>
+      <c r="AC3" s="103"/>
+      <c r="AD3" s="103"/>
+      <c r="AE3" s="103"/>
+      <c r="AF3" s="103"/>
+      <c r="AG3" s="103"/>
+      <c r="AH3" s="103"/>
+      <c r="AI3" s="103"/>
+      <c r="AJ3" s="103"/>
+      <c r="AK3" s="103"/>
+      <c r="AL3" s="103"/>
+      <c r="AM3" s="103"/>
+      <c r="AN3" s="103"/>
+      <c r="AO3" s="103"/>
+      <c r="AP3" s="103"/>
+      <c r="AQ3" s="103"/>
     </row>
     <row r="4" spans="1:44" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F4" s="2" t="s">
@@ -7746,221 +7746,221 @@
       <c r="AQ6" s="32"/>
     </row>
     <row r="7" spans="1:44" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="130" t="s">
+      <c r="A7" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="133" t="s">
+      <c r="B7" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="130" t="s">
+      <c r="C7" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="136" t="s">
+      <c r="D7" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="139" t="s">
+      <c r="E7" s="149" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="142" t="s">
+      <c r="F7" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="143"/>
-      <c r="H7" s="143"/>
-      <c r="I7" s="143"/>
-      <c r="J7" s="143"/>
-      <c r="K7" s="143"/>
-      <c r="L7" s="143"/>
-      <c r="M7" s="143"/>
-      <c r="N7" s="143"/>
-      <c r="O7" s="143"/>
-      <c r="P7" s="143"/>
-      <c r="Q7" s="143"/>
-      <c r="R7" s="143"/>
-      <c r="S7" s="143"/>
-      <c r="T7" s="143"/>
-      <c r="U7" s="143"/>
-      <c r="V7" s="143"/>
-      <c r="W7" s="143"/>
-      <c r="X7" s="143"/>
-      <c r="Y7" s="143"/>
-      <c r="Z7" s="143"/>
-      <c r="AA7" s="143"/>
-      <c r="AB7" s="143"/>
-      <c r="AC7" s="143"/>
-      <c r="AD7" s="143"/>
-      <c r="AE7" s="143"/>
-      <c r="AF7" s="143"/>
-      <c r="AG7" s="143"/>
-      <c r="AH7" s="143"/>
-      <c r="AI7" s="143"/>
-      <c r="AJ7" s="144"/>
-      <c r="AK7" s="145" t="s">
+      <c r="G7" s="153"/>
+      <c r="H7" s="153"/>
+      <c r="I7" s="153"/>
+      <c r="J7" s="153"/>
+      <c r="K7" s="153"/>
+      <c r="L7" s="153"/>
+      <c r="M7" s="153"/>
+      <c r="N7" s="153"/>
+      <c r="O7" s="153"/>
+      <c r="P7" s="153"/>
+      <c r="Q7" s="153"/>
+      <c r="R7" s="153"/>
+      <c r="S7" s="153"/>
+      <c r="T7" s="153"/>
+      <c r="U7" s="153"/>
+      <c r="V7" s="153"/>
+      <c r="W7" s="153"/>
+      <c r="X7" s="153"/>
+      <c r="Y7" s="153"/>
+      <c r="Z7" s="153"/>
+      <c r="AA7" s="153"/>
+      <c r="AB7" s="153"/>
+      <c r="AC7" s="153"/>
+      <c r="AD7" s="153"/>
+      <c r="AE7" s="153"/>
+      <c r="AF7" s="153"/>
+      <c r="AG7" s="153"/>
+      <c r="AH7" s="153"/>
+      <c r="AI7" s="153"/>
+      <c r="AJ7" s="154"/>
+      <c r="AK7" s="155" t="s">
         <v>23</v>
       </c>
-      <c r="AL7" s="145"/>
-      <c r="AM7" s="145"/>
-      <c r="AN7" s="145"/>
-      <c r="AO7" s="145"/>
-      <c r="AP7" s="145"/>
-      <c r="AQ7" s="146"/>
+      <c r="AL7" s="155"/>
+      <c r="AM7" s="155"/>
+      <c r="AN7" s="155"/>
+      <c r="AO7" s="155"/>
+      <c r="AP7" s="155"/>
+      <c r="AQ7" s="156"/>
     </row>
     <row r="8" spans="1:44" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="131"/>
-      <c r="B8" s="134"/>
-      <c r="C8" s="131"/>
-      <c r="D8" s="137"/>
-      <c r="E8" s="140"/>
-      <c r="F8" s="147">
+      <c r="A8" s="141"/>
+      <c r="B8" s="144"/>
+      <c r="C8" s="141"/>
+      <c r="D8" s="147"/>
+      <c r="E8" s="150"/>
+      <c r="F8" s="157">
         <v>1</v>
       </c>
-      <c r="G8" s="114">
+      <c r="G8" s="159">
         <v>2</v>
       </c>
-      <c r="H8" s="114">
+      <c r="H8" s="159">
         <v>3</v>
       </c>
-      <c r="I8" s="114">
+      <c r="I8" s="159">
         <v>4</v>
       </c>
-      <c r="J8" s="114">
+      <c r="J8" s="159">
         <v>5</v>
       </c>
-      <c r="K8" s="114">
+      <c r="K8" s="159">
         <v>6</v>
       </c>
-      <c r="L8" s="114">
+      <c r="L8" s="159">
         <v>7</v>
       </c>
-      <c r="M8" s="114">
+      <c r="M8" s="159">
         <v>8</v>
       </c>
-      <c r="N8" s="114">
+      <c r="N8" s="159">
         <v>9</v>
       </c>
-      <c r="O8" s="114">
+      <c r="O8" s="159">
         <v>10</v>
       </c>
-      <c r="P8" s="114">
+      <c r="P8" s="159">
         <v>11</v>
       </c>
-      <c r="Q8" s="114">
+      <c r="Q8" s="159">
         <v>12</v>
       </c>
-      <c r="R8" s="114">
+      <c r="R8" s="159">
         <v>13</v>
       </c>
-      <c r="S8" s="114">
+      <c r="S8" s="159">
         <v>14</v>
       </c>
-      <c r="T8" s="114">
+      <c r="T8" s="159">
         <v>15</v>
       </c>
-      <c r="U8" s="114">
+      <c r="U8" s="159">
         <v>16</v>
       </c>
-      <c r="V8" s="114">
+      <c r="V8" s="159">
         <v>17</v>
       </c>
-      <c r="W8" s="114">
+      <c r="W8" s="159">
         <v>18</v>
       </c>
-      <c r="X8" s="114">
+      <c r="X8" s="159">
         <v>19</v>
       </c>
-      <c r="Y8" s="114">
+      <c r="Y8" s="159">
         <v>20</v>
       </c>
-      <c r="Z8" s="114">
+      <c r="Z8" s="159">
         <v>21</v>
       </c>
-      <c r="AA8" s="114">
+      <c r="AA8" s="159">
         <v>22</v>
       </c>
-      <c r="AB8" s="114">
+      <c r="AB8" s="159">
         <v>23</v>
       </c>
-      <c r="AC8" s="114">
+      <c r="AC8" s="159">
         <v>24</v>
       </c>
-      <c r="AD8" s="114">
+      <c r="AD8" s="159">
         <v>25</v>
       </c>
-      <c r="AE8" s="114">
+      <c r="AE8" s="159">
         <v>26</v>
       </c>
-      <c r="AF8" s="114">
+      <c r="AF8" s="159">
         <v>27</v>
       </c>
-      <c r="AG8" s="114">
+      <c r="AG8" s="159">
         <v>28</v>
       </c>
-      <c r="AH8" s="114">
+      <c r="AH8" s="159">
         <v>29</v>
       </c>
-      <c r="AI8" s="114">
+      <c r="AI8" s="159">
         <v>30</v>
       </c>
-      <c r="AJ8" s="116">
+      <c r="AJ8" s="164">
         <v>31</v>
       </c>
-      <c r="AK8" s="118" t="s">
+      <c r="AK8" s="166" t="s">
         <v>14</v>
       </c>
-      <c r="AL8" s="120" t="s">
+      <c r="AL8" s="168" t="s">
         <v>13</v>
       </c>
-      <c r="AM8" s="122" t="s">
+      <c r="AM8" s="170" t="s">
         <v>9</v>
       </c>
-      <c r="AN8" s="124" t="s">
+      <c r="AN8" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="AO8" s="125"/>
-      <c r="AP8" s="124" t="s">
+      <c r="AO8" s="173"/>
+      <c r="AP8" s="172" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="126"/>
+      <c r="AQ8" s="174"/>
     </row>
     <row r="9" spans="1:44" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="132"/>
-      <c r="B9" s="135"/>
-      <c r="C9" s="132"/>
-      <c r="D9" s="138"/>
-      <c r="E9" s="141"/>
-      <c r="F9" s="148"/>
-      <c r="G9" s="115"/>
-      <c r="H9" s="115"/>
-      <c r="I9" s="115"/>
-      <c r="J9" s="115"/>
-      <c r="K9" s="115"/>
-      <c r="L9" s="115"/>
-      <c r="M9" s="115"/>
-      <c r="N9" s="115"/>
-      <c r="O9" s="115"/>
-      <c r="P9" s="115"/>
-      <c r="Q9" s="115"/>
-      <c r="R9" s="115"/>
-      <c r="S9" s="115"/>
-      <c r="T9" s="115"/>
-      <c r="U9" s="115"/>
-      <c r="V9" s="115"/>
-      <c r="W9" s="115"/>
-      <c r="X9" s="115"/>
-      <c r="Y9" s="115"/>
-      <c r="Z9" s="115"/>
-      <c r="AA9" s="115"/>
-      <c r="AB9" s="115"/>
-      <c r="AC9" s="115"/>
-      <c r="AD9" s="115"/>
-      <c r="AE9" s="115"/>
-      <c r="AF9" s="115"/>
-      <c r="AG9" s="115"/>
-      <c r="AH9" s="115"/>
-      <c r="AI9" s="115"/>
-      <c r="AJ9" s="117"/>
-      <c r="AK9" s="119"/>
-      <c r="AL9" s="121"/>
-      <c r="AM9" s="123"/>
+      <c r="A9" s="142"/>
+      <c r="B9" s="145"/>
+      <c r="C9" s="142"/>
+      <c r="D9" s="148"/>
+      <c r="E9" s="151"/>
+      <c r="F9" s="158"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160"/>
+      <c r="J9" s="160"/>
+      <c r="K9" s="160"/>
+      <c r="L9" s="160"/>
+      <c r="M9" s="160"/>
+      <c r="N9" s="160"/>
+      <c r="O9" s="160"/>
+      <c r="P9" s="160"/>
+      <c r="Q9" s="160"/>
+      <c r="R9" s="160"/>
+      <c r="S9" s="160"/>
+      <c r="T9" s="160"/>
+      <c r="U9" s="160"/>
+      <c r="V9" s="160"/>
+      <c r="W9" s="160"/>
+      <c r="X9" s="160"/>
+      <c r="Y9" s="160"/>
+      <c r="Z9" s="160"/>
+      <c r="AA9" s="160"/>
+      <c r="AB9" s="160"/>
+      <c r="AC9" s="160"/>
+      <c r="AD9" s="160"/>
+      <c r="AE9" s="160"/>
+      <c r="AF9" s="160"/>
+      <c r="AG9" s="160"/>
+      <c r="AH9" s="160"/>
+      <c r="AI9" s="160"/>
+      <c r="AJ9" s="165"/>
+      <c r="AK9" s="167"/>
+      <c r="AL9" s="169"/>
+      <c r="AM9" s="171"/>
       <c r="AN9" s="47" t="s">
         <v>12</v>
       </c>
@@ -8779,15 +8779,15 @@
       <c r="AH27" s="66"/>
       <c r="AI27" s="66"/>
       <c r="AJ27" s="70"/>
-      <c r="AK27" s="127" t="s">
+      <c r="AK27" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="AL27" s="128"/>
-      <c r="AM27" s="128"/>
-      <c r="AN27" s="128"/>
-      <c r="AO27" s="128"/>
-      <c r="AP27" s="128"/>
-      <c r="AQ27" s="129"/>
+      <c r="AL27" s="176"/>
+      <c r="AM27" s="176"/>
+      <c r="AN27" s="176"/>
+      <c r="AO27" s="176"/>
+      <c r="AP27" s="176"/>
+      <c r="AQ27" s="177"/>
     </row>
     <row r="28" spans="1:43" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="67"/>
@@ -8830,15 +8830,15 @@
       <c r="AH28" s="68"/>
       <c r="AI28" s="68"/>
       <c r="AJ28" s="71"/>
-      <c r="AK28" s="111" t="s">
+      <c r="AK28" s="161" t="s">
         <v>6</v>
       </c>
-      <c r="AL28" s="112"/>
-      <c r="AM28" s="112"/>
-      <c r="AN28" s="112"/>
-      <c r="AO28" s="112"/>
-      <c r="AP28" s="112"/>
-      <c r="AQ28" s="113"/>
+      <c r="AL28" s="162"/>
+      <c r="AM28" s="162"/>
+      <c r="AN28" s="162"/>
+      <c r="AO28" s="162"/>
+      <c r="AP28" s="162"/>
+      <c r="AQ28" s="163"/>
     </row>
     <row r="29" spans="1:43" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F29" s="15"/>
@@ -8916,6 +8916,36 @@
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="AK28:AQ28"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="AN8:AO8"/>
+    <mergeCell ref="AP8:AQ8"/>
+    <mergeCell ref="AK27:AQ27"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
     <mergeCell ref="A3:AQ3"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="B7:B9"/>
@@ -8932,36 +8962,6 @@
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="L8:L9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AK28:AQ28"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="AN8:AO8"/>
-    <mergeCell ref="AP8:AQ8"/>
-    <mergeCell ref="AK27:AQ27"/>
   </mergeCells>
   <pageMargins left="0.27559055118110237" right="0.23622047244094491" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>

--- a/assets/frm-eib04-template.xlsx
+++ b/assets/frm-eib04-template.xlsx
@@ -7542,7 +7542,7 @@
     <mergeCell ref="A7:A9"/>
   </mergeCells>
   <pageMargins left="0.27559055118110237" right="0.23622047244094491" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="77" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="73" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L&amp;"AngsanaUPC,Regular"&amp;14FRM-EIB04 (TP) Rev.03&amp;C&amp;"AngsanaUPC,Regular"&amp;14Effective Date: 31/03/2025 (5Y)&amp;R&amp;"AngsanaUPC,Regular"&amp;14Page &amp;P of &amp;N</oddFooter>
   </headerFooter>

--- a/assets/frm-eib04-template.xlsx
+++ b/assets/frm-eib04-template.xlsx
@@ -7542,7 +7542,7 @@
     <mergeCell ref="A7:A9"/>
   </mergeCells>
   <pageMargins left="0.27559055118110237" right="0.23622047244094491" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="73" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="77" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L&amp;"AngsanaUPC,Regular"&amp;14FRM-EIB04 (TP) Rev.03&amp;C&amp;"AngsanaUPC,Regular"&amp;14Effective Date: 31/03/2025 (5Y)&amp;R&amp;"AngsanaUPC,Regular"&amp;14Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
